--- a/Scorebladen.xlsx
+++ b/Scorebladen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c5821689eb70424b/Python/Manillen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{95CBB5DD-C33F-4433-AF61-DBEE63F661A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51465309-5C95-42C2-B460-DE2CEAC757A8}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{95CBB5DD-C33F-4433-AF61-DBEE63F661A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8843B07-D87A-484D-AFEC-C134CF195E54}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tafel 1" sheetId="4" r:id="rId1"/>
@@ -19,10 +19,10 @@
     <sheet name="Tafel 4" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tafel 1'!$A$1:$T$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Tafel 2'!$A$1:$T$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Tafel 3'!$A$1:$T$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Tafel 4'!$A$1:$T$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tafel 1'!$A$1:$X$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Tafel 2'!$A$1:$X$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Tafel 3'!$A$1:$X$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Tafel 4'!$A$1:$X$29</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -545,32 +545,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="180"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
@@ -587,19 +572,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="180"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -611,15 +611,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -627,6 +618,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -939,7 +939,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.44140625" customWidth="1"/>
@@ -966,71 +966,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="22.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="52"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="40"/>
     </row>
     <row r="2" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="31">
+      <c r="B2" s="42"/>
+      <c r="C2" s="43">
         <v>46113</v>
       </c>
-      <c r="D2" s="32"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="6"/>
       <c r="F2" s="22"/>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="34"/>
-      <c r="I2" s="31">
+      <c r="H2" s="46"/>
+      <c r="I2" s="43">
         <v>46113</v>
       </c>
-      <c r="J2" s="32"/>
+      <c r="J2" s="44"/>
       <c r="K2" s="6"/>
       <c r="L2" s="22"/>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="34"/>
-      <c r="O2" s="31">
+      <c r="N2" s="46"/>
+      <c r="O2" s="43">
         <v>46113</v>
       </c>
-      <c r="P2" s="32"/>
+      <c r="P2" s="44"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="22"/>
-      <c r="S2" s="33" t="s">
+      <c r="S2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="T2" s="34"/>
-      <c r="U2" s="31">
+      <c r="T2" s="46"/>
+      <c r="U2" s="43">
         <v>46113</v>
       </c>
-      <c r="V2" s="32"/>
+      <c r="V2" s="44"/>
       <c r="W2" s="6"/>
     </row>
     <row r="3" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1078,48 +1078,48 @@
       <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="24"/>
       <c r="G4" s="7">
         <v>1</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="39" t="s">
+      <c r="K4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="L4" s="24"/>
       <c r="M4" s="7">
         <v>1</v>
       </c>
-      <c r="N4" s="37" t="s">
+      <c r="N4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-      <c r="Q4" s="39" t="s">
+      <c r="Q4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="R4" s="24"/>
       <c r="S4" s="7">
         <v>1</v>
       </c>
-      <c r="T4" s="37" t="s">
+      <c r="T4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
-      <c r="W4" s="39" t="s">
+      <c r="W4" s="34" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1127,213 +1127,213 @@
       <c r="A5" s="8">
         <v>2</v>
       </c>
-      <c r="B5" s="38"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="3"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="40"/>
+      <c r="E5" s="35"/>
       <c r="F5" s="24"/>
       <c r="G5" s="7">
         <v>2</v>
       </c>
-      <c r="H5" s="38"/>
+      <c r="H5" s="33"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="40"/>
+      <c r="K5" s="35"/>
       <c r="L5" s="24"/>
       <c r="M5" s="7">
         <v>2</v>
       </c>
-      <c r="N5" s="38"/>
+      <c r="N5" s="33"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
-      <c r="Q5" s="40"/>
+      <c r="Q5" s="35"/>
       <c r="R5" s="24"/>
       <c r="S5" s="7">
         <v>2</v>
       </c>
-      <c r="T5" s="38"/>
+      <c r="T5" s="33"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
-      <c r="W5" s="40"/>
+      <c r="W5" s="35"/>
     </row>
     <row r="6" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>3</v>
       </c>
-      <c r="B6" s="38"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="3"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="40"/>
+      <c r="E6" s="35"/>
       <c r="F6" s="24"/>
       <c r="G6" s="7">
         <v>3</v>
       </c>
-      <c r="H6" s="38"/>
+      <c r="H6" s="33"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="40"/>
+      <c r="K6" s="35"/>
       <c r="L6" s="24"/>
       <c r="M6" s="7">
         <v>3</v>
       </c>
-      <c r="N6" s="38"/>
+      <c r="N6" s="33"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="40"/>
+      <c r="Q6" s="35"/>
       <c r="R6" s="24"/>
       <c r="S6" s="7">
         <v>3</v>
       </c>
-      <c r="T6" s="38"/>
+      <c r="T6" s="33"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
-      <c r="W6" s="40"/>
+      <c r="W6" s="35"/>
     </row>
     <row r="7" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>4</v>
       </c>
-      <c r="B7" s="38"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="3"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="40"/>
+      <c r="E7" s="35"/>
       <c r="F7" s="24"/>
       <c r="G7" s="7">
         <v>4</v>
       </c>
-      <c r="H7" s="38"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="40"/>
+      <c r="K7" s="35"/>
       <c r="L7" s="24"/>
       <c r="M7" s="7">
         <v>4</v>
       </c>
-      <c r="N7" s="38"/>
+      <c r="N7" s="33"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="40"/>
+      <c r="Q7" s="35"/>
       <c r="R7" s="24"/>
       <c r="S7" s="7">
         <v>4</v>
       </c>
-      <c r="T7" s="38"/>
+      <c r="T7" s="33"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
-      <c r="W7" s="40"/>
+      <c r="W7" s="35"/>
     </row>
     <row r="8" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>5</v>
       </c>
-      <c r="B8" s="38"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="3"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="40"/>
+      <c r="E8" s="35"/>
       <c r="F8" s="24"/>
       <c r="G8" s="7">
         <v>5</v>
       </c>
-      <c r="H8" s="38"/>
+      <c r="H8" s="33"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="40"/>
+      <c r="K8" s="35"/>
       <c r="L8" s="24"/>
       <c r="M8" s="7">
         <v>5</v>
       </c>
-      <c r="N8" s="38"/>
+      <c r="N8" s="33"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
-      <c r="Q8" s="40"/>
+      <c r="Q8" s="35"/>
       <c r="R8" s="24"/>
       <c r="S8" s="7">
         <v>5</v>
       </c>
-      <c r="T8" s="38"/>
+      <c r="T8" s="33"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
-      <c r="W8" s="40"/>
+      <c r="W8" s="35"/>
     </row>
     <row r="9" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>6</v>
       </c>
-      <c r="B9" s="38"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="3"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="40"/>
+      <c r="E9" s="35"/>
       <c r="F9" s="24"/>
       <c r="G9" s="7">
         <v>6</v>
       </c>
-      <c r="H9" s="38"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="40"/>
+      <c r="K9" s="35"/>
       <c r="L9" s="24"/>
       <c r="M9" s="7">
         <v>6</v>
       </c>
-      <c r="N9" s="38"/>
+      <c r="N9" s="33"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-      <c r="Q9" s="40"/>
+      <c r="Q9" s="35"/>
       <c r="R9" s="24"/>
       <c r="S9" s="7">
         <v>6</v>
       </c>
-      <c r="T9" s="38"/>
+      <c r="T9" s="33"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
-      <c r="W9" s="40"/>
+      <c r="W9" s="35"/>
     </row>
     <row r="10" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>7</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="37" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="25"/>
       <c r="G10" s="7">
         <v>7</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="H10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="28" t="s">
+      <c r="K10" s="37" t="s">
         <v>4</v>
       </c>
       <c r="L10" s="25"/>
       <c r="M10" s="8">
         <v>7</v>
       </c>
-      <c r="N10" s="41" t="s">
+      <c r="N10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="4"/>
-      <c r="Q10" s="28" t="s">
+      <c r="Q10" s="37" t="s">
         <v>4</v>
       </c>
       <c r="R10" s="25"/>
       <c r="S10" s="7">
         <v>7</v>
       </c>
-      <c r="T10" s="41" t="s">
+      <c r="T10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="U10" s="1"/>
       <c r="V10" s="4"/>
-      <c r="W10" s="28" t="s">
+      <c r="W10" s="37" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1341,232 +1341,232 @@
       <c r="A11" s="8">
         <v>8</v>
       </c>
-      <c r="B11" s="41"/>
+      <c r="B11" s="36"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="28"/>
+      <c r="E11" s="37"/>
       <c r="F11" s="25"/>
       <c r="G11" s="7">
         <v>8</v>
       </c>
-      <c r="H11" s="41"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="1"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="28"/>
+      <c r="K11" s="37"/>
       <c r="L11" s="25"/>
       <c r="M11" s="8">
         <v>8</v>
       </c>
-      <c r="N11" s="41"/>
+      <c r="N11" s="36"/>
       <c r="O11" s="3"/>
       <c r="P11" s="4"/>
-      <c r="Q11" s="28"/>
+      <c r="Q11" s="37"/>
       <c r="R11" s="25"/>
       <c r="S11" s="7">
         <v>8</v>
       </c>
-      <c r="T11" s="41"/>
+      <c r="T11" s="36"/>
       <c r="U11" s="1"/>
       <c r="V11" s="4"/>
-      <c r="W11" s="28"/>
+      <c r="W11" s="37"/>
     </row>
     <row r="12" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>9</v>
       </c>
-      <c r="B12" s="41"/>
+      <c r="B12" s="36"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="28"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="25"/>
       <c r="G12" s="7">
         <v>9</v>
       </c>
-      <c r="H12" s="41"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="1"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="28"/>
+      <c r="K12" s="37"/>
       <c r="L12" s="25"/>
       <c r="M12" s="8">
         <v>9</v>
       </c>
-      <c r="N12" s="41"/>
+      <c r="N12" s="36"/>
       <c r="O12" s="3"/>
       <c r="P12" s="4"/>
-      <c r="Q12" s="28"/>
+      <c r="Q12" s="37"/>
       <c r="R12" s="25"/>
       <c r="S12" s="7">
         <v>9</v>
       </c>
-      <c r="T12" s="41"/>
+      <c r="T12" s="36"/>
       <c r="U12" s="1"/>
       <c r="V12" s="4"/>
-      <c r="W12" s="28"/>
+      <c r="W12" s="37"/>
     </row>
     <row r="13" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>10</v>
       </c>
-      <c r="B13" s="41"/>
+      <c r="B13" s="36"/>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="28"/>
+      <c r="E13" s="37"/>
       <c r="F13" s="25"/>
       <c r="G13" s="7">
         <v>10</v>
       </c>
-      <c r="H13" s="41"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="1"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="28"/>
+      <c r="K13" s="37"/>
       <c r="L13" s="25"/>
       <c r="M13" s="8">
         <v>10</v>
       </c>
-      <c r="N13" s="41"/>
+      <c r="N13" s="36"/>
       <c r="O13" s="3"/>
       <c r="P13" s="4"/>
-      <c r="Q13" s="28"/>
+      <c r="Q13" s="37"/>
       <c r="R13" s="25"/>
       <c r="S13" s="7">
         <v>10</v>
       </c>
-      <c r="T13" s="41"/>
+      <c r="T13" s="36"/>
       <c r="U13" s="1"/>
       <c r="V13" s="4"/>
-      <c r="W13" s="28"/>
+      <c r="W13" s="37"/>
     </row>
     <row r="14" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>11</v>
       </c>
-      <c r="B14" s="41"/>
+      <c r="B14" s="36"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="28"/>
+      <c r="E14" s="37"/>
       <c r="F14" s="25"/>
       <c r="G14" s="7">
         <v>11</v>
       </c>
-      <c r="H14" s="41"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="1"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="28"/>
+      <c r="K14" s="37"/>
       <c r="L14" s="25"/>
       <c r="M14" s="8">
         <v>11</v>
       </c>
-      <c r="N14" s="41"/>
+      <c r="N14" s="36"/>
       <c r="O14" s="3"/>
       <c r="P14" s="4"/>
-      <c r="Q14" s="28"/>
+      <c r="Q14" s="37"/>
       <c r="R14" s="25"/>
       <c r="S14" s="7">
         <v>11</v>
       </c>
-      <c r="T14" s="41"/>
+      <c r="T14" s="36"/>
       <c r="U14" s="1"/>
       <c r="V14" s="4"/>
-      <c r="W14" s="28"/>
+      <c r="W14" s="37"/>
     </row>
     <row r="15" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>12</v>
       </c>
-      <c r="B15" s="41"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="28"/>
+      <c r="E15" s="37"/>
       <c r="F15" s="25"/>
       <c r="G15" s="7">
         <v>12</v>
       </c>
-      <c r="H15" s="41"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="1"/>
       <c r="J15" s="4"/>
-      <c r="K15" s="28"/>
+      <c r="K15" s="37"/>
       <c r="L15" s="25"/>
       <c r="M15" s="8">
         <v>12</v>
       </c>
-      <c r="N15" s="41"/>
+      <c r="N15" s="36"/>
       <c r="O15" s="3"/>
       <c r="P15" s="4"/>
-      <c r="Q15" s="28"/>
+      <c r="Q15" s="37"/>
       <c r="R15" s="25"/>
       <c r="S15" s="7">
         <v>12</v>
       </c>
-      <c r="T15" s="41"/>
+      <c r="T15" s="36"/>
       <c r="U15" s="1"/>
       <c r="V15" s="4"/>
-      <c r="W15" s="28"/>
+      <c r="W15" s="37"/>
     </row>
     <row r="16" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>13</v>
       </c>
-      <c r="B16" s="41"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="3"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="28"/>
+      <c r="E16" s="37"/>
       <c r="F16" s="25"/>
       <c r="G16" s="7">
         <v>13</v>
       </c>
-      <c r="H16" s="41"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="1"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="28"/>
+      <c r="K16" s="37"/>
       <c r="L16" s="25"/>
       <c r="M16" s="8">
         <v>13</v>
       </c>
-      <c r="N16" s="41"/>
+      <c r="N16" s="36"/>
       <c r="O16" s="3"/>
       <c r="P16" s="4"/>
-      <c r="Q16" s="28"/>
+      <c r="Q16" s="37"/>
       <c r="R16" s="25"/>
       <c r="S16" s="7">
         <v>13</v>
       </c>
-      <c r="T16" s="41"/>
+      <c r="T16" s="36"/>
       <c r="U16" s="1"/>
       <c r="V16" s="4"/>
-      <c r="W16" s="28"/>
+      <c r="W16" s="37"/>
     </row>
     <row r="17" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>14</v>
       </c>
-      <c r="B17" s="41"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="28"/>
+      <c r="E17" s="37"/>
       <c r="F17" s="25"/>
       <c r="G17" s="7">
         <v>14</v>
       </c>
-      <c r="H17" s="41"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="1"/>
       <c r="J17" s="4"/>
-      <c r="K17" s="28"/>
+      <c r="K17" s="37"/>
       <c r="L17" s="25"/>
       <c r="M17" s="8">
         <v>14</v>
       </c>
-      <c r="N17" s="41"/>
+      <c r="N17" s="36"/>
       <c r="O17" s="3"/>
       <c r="P17" s="4"/>
-      <c r="Q17" s="28"/>
+      <c r="Q17" s="37"/>
       <c r="R17" s="25"/>
       <c r="S17" s="7">
         <v>14</v>
       </c>
-      <c r="T17" s="41"/>
+      <c r="T17" s="36"/>
       <c r="U17" s="1"/>
       <c r="V17" s="4"/>
-      <c r="W17" s="28"/>
+      <c r="W17" s="37"/>
     </row>
     <row r="18" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
@@ -1621,48 +1621,48 @@
       <c r="A19" s="8">
         <v>16</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="30" t="s">
         <v>6</v>
       </c>
       <c r="F19" s="26"/>
       <c r="G19" s="7">
         <v>16</v>
       </c>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="4"/>
-      <c r="K19" s="29" t="s">
+      <c r="K19" s="30" t="s">
         <v>6</v>
       </c>
       <c r="L19" s="26"/>
       <c r="M19" s="8">
         <v>16</v>
       </c>
-      <c r="N19" s="42" t="s">
+      <c r="N19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="4"/>
-      <c r="Q19" s="29" t="s">
+      <c r="Q19" s="30" t="s">
         <v>6</v>
       </c>
       <c r="R19" s="26"/>
       <c r="S19" s="7">
         <v>16</v>
       </c>
-      <c r="T19" s="42" t="s">
+      <c r="T19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="U19" s="1"/>
       <c r="V19" s="4"/>
-      <c r="W19" s="29" t="s">
+      <c r="W19" s="30" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1670,309 +1670,313 @@
       <c r="A20" s="8">
         <v>17</v>
       </c>
-      <c r="B20" s="42"/>
+      <c r="B20" s="28"/>
       <c r="C20" s="3"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="29"/>
+      <c r="E20" s="30"/>
       <c r="F20" s="26"/>
       <c r="G20" s="7">
         <v>17</v>
       </c>
-      <c r="H20" s="42"/>
+      <c r="H20" s="28"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-      <c r="K20" s="29"/>
+      <c r="K20" s="30"/>
       <c r="L20" s="26"/>
       <c r="M20" s="7">
         <v>17</v>
       </c>
-      <c r="N20" s="42"/>
+      <c r="N20" s="28"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="29"/>
+      <c r="Q20" s="30"/>
       <c r="R20" s="26"/>
       <c r="S20" s="7">
         <v>17</v>
       </c>
-      <c r="T20" s="42"/>
+      <c r="T20" s="28"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
-      <c r="W20" s="29"/>
+      <c r="W20" s="30"/>
     </row>
     <row r="21" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>18</v>
       </c>
-      <c r="B21" s="42"/>
+      <c r="B21" s="28"/>
       <c r="C21" s="3"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="29"/>
+      <c r="E21" s="30"/>
       <c r="F21" s="26"/>
       <c r="G21" s="7">
         <v>18</v>
       </c>
-      <c r="H21" s="42"/>
+      <c r="H21" s="28"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="29"/>
+      <c r="K21" s="30"/>
       <c r="L21" s="26"/>
       <c r="M21" s="7">
         <v>18</v>
       </c>
-      <c r="N21" s="42"/>
+      <c r="N21" s="28"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="29"/>
+      <c r="Q21" s="30"/>
       <c r="R21" s="26"/>
       <c r="S21" s="7">
         <v>18</v>
       </c>
-      <c r="T21" s="42"/>
+      <c r="T21" s="28"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
-      <c r="W21" s="29"/>
+      <c r="W21" s="30"/>
     </row>
     <row r="22" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>19</v>
       </c>
-      <c r="B22" s="42"/>
+      <c r="B22" s="28"/>
       <c r="C22" s="3"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="29"/>
+      <c r="E22" s="30"/>
       <c r="F22" s="26"/>
       <c r="G22" s="7">
         <v>19</v>
       </c>
-      <c r="H22" s="42"/>
+      <c r="H22" s="28"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-      <c r="K22" s="29"/>
+      <c r="K22" s="30"/>
       <c r="L22" s="26"/>
       <c r="M22" s="7">
         <v>19</v>
       </c>
-      <c r="N22" s="42"/>
+      <c r="N22" s="28"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
-      <c r="Q22" s="29"/>
+      <c r="Q22" s="30"/>
       <c r="R22" s="26"/>
       <c r="S22" s="7">
         <v>19</v>
       </c>
-      <c r="T22" s="42"/>
+      <c r="T22" s="28"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
-      <c r="W22" s="29"/>
+      <c r="W22" s="30"/>
     </row>
     <row r="23" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>20</v>
       </c>
-      <c r="B23" s="42"/>
+      <c r="B23" s="28"/>
       <c r="C23" s="3"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="29"/>
+      <c r="E23" s="30"/>
       <c r="F23" s="26"/>
       <c r="G23" s="7">
         <v>20</v>
       </c>
-      <c r="H23" s="42"/>
+      <c r="H23" s="28"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="29"/>
+      <c r="K23" s="30"/>
       <c r="L23" s="26"/>
       <c r="M23" s="7">
         <v>20</v>
       </c>
-      <c r="N23" s="42"/>
+      <c r="N23" s="28"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="29"/>
+      <c r="Q23" s="30"/>
       <c r="R23" s="26"/>
       <c r="S23" s="7">
         <v>20</v>
       </c>
-      <c r="T23" s="42"/>
+      <c r="T23" s="28"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
-      <c r="W23" s="29"/>
+      <c r="W23" s="30"/>
     </row>
     <row r="24" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>21</v>
       </c>
-      <c r="B24" s="42"/>
+      <c r="B24" s="28"/>
       <c r="C24" s="3"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="29"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="26"/>
       <c r="G24" s="7">
         <v>21</v>
       </c>
-      <c r="H24" s="42"/>
+      <c r="H24" s="28"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-      <c r="K24" s="29"/>
+      <c r="K24" s="30"/>
       <c r="L24" s="26"/>
       <c r="M24" s="7">
         <v>21</v>
       </c>
-      <c r="N24" s="42"/>
+      <c r="N24" s="28"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="29"/>
+      <c r="Q24" s="30"/>
       <c r="R24" s="26"/>
       <c r="S24" s="7">
         <v>21</v>
       </c>
-      <c r="T24" s="42"/>
+      <c r="T24" s="28"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
-      <c r="W24" s="29"/>
+      <c r="W24" s="30"/>
     </row>
     <row r="25" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>22</v>
       </c>
-      <c r="B25" s="42"/>
+      <c r="B25" s="28"/>
       <c r="C25" s="3"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="29"/>
+      <c r="E25" s="30"/>
       <c r="F25" s="26"/>
       <c r="G25" s="7">
         <v>22</v>
       </c>
-      <c r="H25" s="42"/>
+      <c r="H25" s="28"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="29"/>
+      <c r="K25" s="30"/>
       <c r="L25" s="26"/>
       <c r="M25" s="7">
         <v>22</v>
       </c>
-      <c r="N25" s="42"/>
+      <c r="N25" s="28"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="29"/>
+      <c r="Q25" s="30"/>
       <c r="R25" s="26"/>
       <c r="S25" s="7">
         <v>22</v>
       </c>
-      <c r="T25" s="42"/>
+      <c r="T25" s="28"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
-      <c r="W25" s="29"/>
+      <c r="W25" s="30"/>
     </row>
     <row r="26" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>23</v>
       </c>
-      <c r="B26" s="42"/>
+      <c r="B26" s="28"/>
       <c r="C26" s="3"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="29"/>
+      <c r="E26" s="30"/>
       <c r="F26" s="26"/>
       <c r="G26" s="7">
         <v>23</v>
       </c>
-      <c r="H26" s="42"/>
+      <c r="H26" s="28"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="29"/>
+      <c r="K26" s="30"/>
       <c r="L26" s="26"/>
       <c r="M26" s="7">
         <v>23</v>
       </c>
-      <c r="N26" s="42"/>
+      <c r="N26" s="28"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="29"/>
+      <c r="Q26" s="30"/>
       <c r="R26" s="26"/>
       <c r="S26" s="7">
         <v>23</v>
       </c>
-      <c r="T26" s="42"/>
+      <c r="T26" s="28"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
-      <c r="W26" s="29"/>
+      <c r="W26" s="30"/>
     </row>
     <row r="27" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>24</v>
       </c>
-      <c r="B27" s="42"/>
+      <c r="B27" s="28"/>
       <c r="C27" s="3"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="29"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="26"/>
       <c r="G27" s="7">
         <v>24</v>
       </c>
-      <c r="H27" s="42"/>
+      <c r="H27" s="28"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="29"/>
+      <c r="K27" s="30"/>
       <c r="L27" s="26"/>
       <c r="M27" s="7">
         <v>24</v>
       </c>
-      <c r="N27" s="42"/>
+      <c r="N27" s="28"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="29"/>
+      <c r="Q27" s="30"/>
       <c r="R27" s="26"/>
       <c r="S27" s="7">
         <v>24</v>
       </c>
-      <c r="T27" s="42"/>
+      <c r="T27" s="28"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
-      <c r="W27" s="29"/>
+      <c r="W27" s="30"/>
     </row>
     <row r="28" spans="1:23" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11">
         <v>25</v>
       </c>
-      <c r="B28" s="43"/>
+      <c r="B28" s="29"/>
       <c r="C28" s="12"/>
       <c r="D28" s="10"/>
-      <c r="E28" s="30"/>
+      <c r="E28" s="31"/>
       <c r="F28" s="27"/>
       <c r="G28" s="9">
         <v>25</v>
       </c>
-      <c r="H28" s="43"/>
+      <c r="H28" s="29"/>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
-      <c r="K28" s="30"/>
+      <c r="K28" s="31"/>
       <c r="L28" s="27"/>
       <c r="M28" s="9">
         <v>25</v>
       </c>
-      <c r="N28" s="43"/>
+      <c r="N28" s="29"/>
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
-      <c r="Q28" s="30"/>
+      <c r="Q28" s="31"/>
       <c r="R28" s="27"/>
       <c r="S28" s="9">
         <v>25</v>
       </c>
-      <c r="T28" s="43"/>
+      <c r="T28" s="29"/>
       <c r="U28" s="10"/>
       <c r="V28" s="10"/>
-      <c r="W28" s="30"/>
+      <c r="W28" s="31"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="V29" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="T19:T28"/>
-    <mergeCell ref="W19:W28"/>
-    <mergeCell ref="B19:B28"/>
-    <mergeCell ref="E19:E28"/>
-    <mergeCell ref="H19:H28"/>
-    <mergeCell ref="K19:K28"/>
-    <mergeCell ref="N19:N28"/>
-    <mergeCell ref="Q19:Q28"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
     <mergeCell ref="T4:T9"/>
     <mergeCell ref="W4:W9"/>
     <mergeCell ref="B10:B17"/>
@@ -1989,18 +1993,17 @@
     <mergeCell ref="K4:K9"/>
     <mergeCell ref="N4:N9"/>
     <mergeCell ref="Q4:Q9"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="T19:T28"/>
+    <mergeCell ref="W19:W28"/>
+    <mergeCell ref="B19:B28"/>
+    <mergeCell ref="E19:E28"/>
+    <mergeCell ref="H19:H28"/>
+    <mergeCell ref="K19:K28"/>
+    <mergeCell ref="N19:N28"/>
+    <mergeCell ref="Q19:Q28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="75" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="60" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2063,44 +2066,44 @@
       <c r="W1" s="49"/>
     </row>
     <row r="2" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="31">
+      <c r="B2" s="42"/>
+      <c r="C2" s="43">
         <v>46113</v>
       </c>
-      <c r="D2" s="32"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="6"/>
       <c r="F2" s="22"/>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="34"/>
-      <c r="I2" s="31">
+      <c r="H2" s="46"/>
+      <c r="I2" s="43">
         <v>46113</v>
       </c>
-      <c r="J2" s="32"/>
+      <c r="J2" s="44"/>
       <c r="K2" s="6"/>
       <c r="L2" s="22"/>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="34"/>
-      <c r="O2" s="31">
+      <c r="N2" s="46"/>
+      <c r="O2" s="43">
         <v>46113</v>
       </c>
-      <c r="P2" s="32"/>
+      <c r="P2" s="44"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="22"/>
-      <c r="S2" s="33" t="s">
+      <c r="S2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="T2" s="34"/>
-      <c r="U2" s="31">
+      <c r="T2" s="46"/>
+      <c r="U2" s="43">
         <v>46113</v>
       </c>
-      <c r="V2" s="32"/>
+      <c r="V2" s="44"/>
       <c r="W2" s="6"/>
     </row>
     <row r="3" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -2148,48 +2151,48 @@
       <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="24"/>
       <c r="G4" s="7">
         <v>1</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="39" t="s">
+      <c r="K4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="L4" s="24"/>
       <c r="M4" s="7">
         <v>1</v>
       </c>
-      <c r="N4" s="37" t="s">
+      <c r="N4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-      <c r="Q4" s="39" t="s">
+      <c r="Q4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="R4" s="24"/>
       <c r="S4" s="7">
         <v>1</v>
       </c>
-      <c r="T4" s="37" t="s">
+      <c r="T4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
-      <c r="W4" s="39" t="s">
+      <c r="W4" s="34" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2197,213 +2200,213 @@
       <c r="A5" s="8">
         <v>2</v>
       </c>
-      <c r="B5" s="38"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="3"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="40"/>
+      <c r="E5" s="35"/>
       <c r="F5" s="24"/>
       <c r="G5" s="7">
         <v>2</v>
       </c>
-      <c r="H5" s="38"/>
+      <c r="H5" s="33"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="40"/>
+      <c r="K5" s="35"/>
       <c r="L5" s="24"/>
       <c r="M5" s="7">
         <v>2</v>
       </c>
-      <c r="N5" s="38"/>
+      <c r="N5" s="33"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
-      <c r="Q5" s="40"/>
+      <c r="Q5" s="35"/>
       <c r="R5" s="24"/>
       <c r="S5" s="7">
         <v>2</v>
       </c>
-      <c r="T5" s="38"/>
+      <c r="T5" s="33"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
-      <c r="W5" s="40"/>
+      <c r="W5" s="35"/>
     </row>
     <row r="6" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>3</v>
       </c>
-      <c r="B6" s="38"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="3"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="40"/>
+      <c r="E6" s="35"/>
       <c r="F6" s="24"/>
       <c r="G6" s="7">
         <v>3</v>
       </c>
-      <c r="H6" s="38"/>
+      <c r="H6" s="33"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="40"/>
+      <c r="K6" s="35"/>
       <c r="L6" s="24"/>
       <c r="M6" s="7">
         <v>3</v>
       </c>
-      <c r="N6" s="38"/>
+      <c r="N6" s="33"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="40"/>
+      <c r="Q6" s="35"/>
       <c r="R6" s="24"/>
       <c r="S6" s="7">
         <v>3</v>
       </c>
-      <c r="T6" s="38"/>
+      <c r="T6" s="33"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
-      <c r="W6" s="40"/>
+      <c r="W6" s="35"/>
     </row>
     <row r="7" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>4</v>
       </c>
-      <c r="B7" s="38"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="3"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="40"/>
+      <c r="E7" s="35"/>
       <c r="F7" s="24"/>
       <c r="G7" s="7">
         <v>4</v>
       </c>
-      <c r="H7" s="38"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="40"/>
+      <c r="K7" s="35"/>
       <c r="L7" s="24"/>
       <c r="M7" s="7">
         <v>4</v>
       </c>
-      <c r="N7" s="38"/>
+      <c r="N7" s="33"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="40"/>
+      <c r="Q7" s="35"/>
       <c r="R7" s="24"/>
       <c r="S7" s="7">
         <v>4</v>
       </c>
-      <c r="T7" s="38"/>
+      <c r="T7" s="33"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
-      <c r="W7" s="40"/>
+      <c r="W7" s="35"/>
     </row>
     <row r="8" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>5</v>
       </c>
-      <c r="B8" s="38"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="3"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="40"/>
+      <c r="E8" s="35"/>
       <c r="F8" s="24"/>
       <c r="G8" s="7">
         <v>5</v>
       </c>
-      <c r="H8" s="38"/>
+      <c r="H8" s="33"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="40"/>
+      <c r="K8" s="35"/>
       <c r="L8" s="24"/>
       <c r="M8" s="7">
         <v>5</v>
       </c>
-      <c r="N8" s="38"/>
+      <c r="N8" s="33"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
-      <c r="Q8" s="40"/>
+      <c r="Q8" s="35"/>
       <c r="R8" s="24"/>
       <c r="S8" s="7">
         <v>5</v>
       </c>
-      <c r="T8" s="38"/>
+      <c r="T8" s="33"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
-      <c r="W8" s="40"/>
+      <c r="W8" s="35"/>
     </row>
     <row r="9" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>6</v>
       </c>
-      <c r="B9" s="38"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="3"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="40"/>
+      <c r="E9" s="35"/>
       <c r="F9" s="24"/>
       <c r="G9" s="7">
         <v>6</v>
       </c>
-      <c r="H9" s="38"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="40"/>
+      <c r="K9" s="35"/>
       <c r="L9" s="24"/>
       <c r="M9" s="7">
         <v>6</v>
       </c>
-      <c r="N9" s="38"/>
+      <c r="N9" s="33"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-      <c r="Q9" s="40"/>
+      <c r="Q9" s="35"/>
       <c r="R9" s="24"/>
       <c r="S9" s="7">
         <v>6</v>
       </c>
-      <c r="T9" s="38"/>
+      <c r="T9" s="33"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
-      <c r="W9" s="40"/>
+      <c r="W9" s="35"/>
     </row>
     <row r="10" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>7</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="37" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="25"/>
       <c r="G10" s="7">
         <v>7</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="H10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="28" t="s">
+      <c r="K10" s="37" t="s">
         <v>4</v>
       </c>
       <c r="L10" s="25"/>
       <c r="M10" s="8">
         <v>7</v>
       </c>
-      <c r="N10" s="41" t="s">
+      <c r="N10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="4"/>
-      <c r="Q10" s="28" t="s">
+      <c r="Q10" s="37" t="s">
         <v>4</v>
       </c>
       <c r="R10" s="25"/>
       <c r="S10" s="7">
         <v>7</v>
       </c>
-      <c r="T10" s="41" t="s">
+      <c r="T10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="U10" s="1"/>
       <c r="V10" s="4"/>
-      <c r="W10" s="28" t="s">
+      <c r="W10" s="37" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2411,232 +2414,232 @@
       <c r="A11" s="8">
         <v>8</v>
       </c>
-      <c r="B11" s="41"/>
+      <c r="B11" s="36"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="28"/>
+      <c r="E11" s="37"/>
       <c r="F11" s="25"/>
       <c r="G11" s="7">
         <v>8</v>
       </c>
-      <c r="H11" s="41"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="1"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="28"/>
+      <c r="K11" s="37"/>
       <c r="L11" s="25"/>
       <c r="M11" s="8">
         <v>8</v>
       </c>
-      <c r="N11" s="41"/>
+      <c r="N11" s="36"/>
       <c r="O11" s="3"/>
       <c r="P11" s="4"/>
-      <c r="Q11" s="28"/>
+      <c r="Q11" s="37"/>
       <c r="R11" s="25"/>
       <c r="S11" s="7">
         <v>8</v>
       </c>
-      <c r="T11" s="41"/>
+      <c r="T11" s="36"/>
       <c r="U11" s="1"/>
       <c r="V11" s="4"/>
-      <c r="W11" s="28"/>
+      <c r="W11" s="37"/>
     </row>
     <row r="12" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>9</v>
       </c>
-      <c r="B12" s="41"/>
+      <c r="B12" s="36"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="28"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="25"/>
       <c r="G12" s="7">
         <v>9</v>
       </c>
-      <c r="H12" s="41"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="1"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="28"/>
+      <c r="K12" s="37"/>
       <c r="L12" s="25"/>
       <c r="M12" s="8">
         <v>9</v>
       </c>
-      <c r="N12" s="41"/>
+      <c r="N12" s="36"/>
       <c r="O12" s="3"/>
       <c r="P12" s="4"/>
-      <c r="Q12" s="28"/>
+      <c r="Q12" s="37"/>
       <c r="R12" s="25"/>
       <c r="S12" s="7">
         <v>9</v>
       </c>
-      <c r="T12" s="41"/>
+      <c r="T12" s="36"/>
       <c r="U12" s="1"/>
       <c r="V12" s="4"/>
-      <c r="W12" s="28"/>
+      <c r="W12" s="37"/>
     </row>
     <row r="13" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>10</v>
       </c>
-      <c r="B13" s="41"/>
+      <c r="B13" s="36"/>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="28"/>
+      <c r="E13" s="37"/>
       <c r="F13" s="25"/>
       <c r="G13" s="7">
         <v>10</v>
       </c>
-      <c r="H13" s="41"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="1"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="28"/>
+      <c r="K13" s="37"/>
       <c r="L13" s="25"/>
       <c r="M13" s="8">
         <v>10</v>
       </c>
-      <c r="N13" s="41"/>
+      <c r="N13" s="36"/>
       <c r="O13" s="3"/>
       <c r="P13" s="4"/>
-      <c r="Q13" s="28"/>
+      <c r="Q13" s="37"/>
       <c r="R13" s="25"/>
       <c r="S13" s="7">
         <v>10</v>
       </c>
-      <c r="T13" s="41"/>
+      <c r="T13" s="36"/>
       <c r="U13" s="1"/>
       <c r="V13" s="4"/>
-      <c r="W13" s="28"/>
+      <c r="W13" s="37"/>
     </row>
     <row r="14" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>11</v>
       </c>
-      <c r="B14" s="41"/>
+      <c r="B14" s="36"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="28"/>
+      <c r="E14" s="37"/>
       <c r="F14" s="25"/>
       <c r="G14" s="7">
         <v>11</v>
       </c>
-      <c r="H14" s="41"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="1"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="28"/>
+      <c r="K14" s="37"/>
       <c r="L14" s="25"/>
       <c r="M14" s="8">
         <v>11</v>
       </c>
-      <c r="N14" s="41"/>
+      <c r="N14" s="36"/>
       <c r="O14" s="3"/>
       <c r="P14" s="4"/>
-      <c r="Q14" s="28"/>
+      <c r="Q14" s="37"/>
       <c r="R14" s="25"/>
       <c r="S14" s="7">
         <v>11</v>
       </c>
-      <c r="T14" s="41"/>
+      <c r="T14" s="36"/>
       <c r="U14" s="1"/>
       <c r="V14" s="4"/>
-      <c r="W14" s="28"/>
+      <c r="W14" s="37"/>
     </row>
     <row r="15" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>12</v>
       </c>
-      <c r="B15" s="41"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="28"/>
+      <c r="E15" s="37"/>
       <c r="F15" s="25"/>
       <c r="G15" s="7">
         <v>12</v>
       </c>
-      <c r="H15" s="41"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="1"/>
       <c r="J15" s="4"/>
-      <c r="K15" s="28"/>
+      <c r="K15" s="37"/>
       <c r="L15" s="25"/>
       <c r="M15" s="8">
         <v>12</v>
       </c>
-      <c r="N15" s="41"/>
+      <c r="N15" s="36"/>
       <c r="O15" s="3"/>
       <c r="P15" s="4"/>
-      <c r="Q15" s="28"/>
+      <c r="Q15" s="37"/>
       <c r="R15" s="25"/>
       <c r="S15" s="7">
         <v>12</v>
       </c>
-      <c r="T15" s="41"/>
+      <c r="T15" s="36"/>
       <c r="U15" s="1"/>
       <c r="V15" s="4"/>
-      <c r="W15" s="28"/>
+      <c r="W15" s="37"/>
     </row>
     <row r="16" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>13</v>
       </c>
-      <c r="B16" s="41"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="3"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="28"/>
+      <c r="E16" s="37"/>
       <c r="F16" s="25"/>
       <c r="G16" s="7">
         <v>13</v>
       </c>
-      <c r="H16" s="41"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="1"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="28"/>
+      <c r="K16" s="37"/>
       <c r="L16" s="25"/>
       <c r="M16" s="8">
         <v>13</v>
       </c>
-      <c r="N16" s="41"/>
+      <c r="N16" s="36"/>
       <c r="O16" s="3"/>
       <c r="P16" s="4"/>
-      <c r="Q16" s="28"/>
+      <c r="Q16" s="37"/>
       <c r="R16" s="25"/>
       <c r="S16" s="7">
         <v>13</v>
       </c>
-      <c r="T16" s="41"/>
+      <c r="T16" s="36"/>
       <c r="U16" s="1"/>
       <c r="V16" s="4"/>
-      <c r="W16" s="28"/>
+      <c r="W16" s="37"/>
     </row>
     <row r="17" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>14</v>
       </c>
-      <c r="B17" s="41"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="28"/>
+      <c r="E17" s="37"/>
       <c r="F17" s="25"/>
       <c r="G17" s="7">
         <v>14</v>
       </c>
-      <c r="H17" s="41"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="1"/>
       <c r="J17" s="4"/>
-      <c r="K17" s="28"/>
+      <c r="K17" s="37"/>
       <c r="L17" s="25"/>
       <c r="M17" s="8">
         <v>14</v>
       </c>
-      <c r="N17" s="41"/>
+      <c r="N17" s="36"/>
       <c r="O17" s="3"/>
       <c r="P17" s="4"/>
-      <c r="Q17" s="28"/>
+      <c r="Q17" s="37"/>
       <c r="R17" s="25"/>
       <c r="S17" s="7">
         <v>14</v>
       </c>
-      <c r="T17" s="41"/>
+      <c r="T17" s="36"/>
       <c r="U17" s="1"/>
       <c r="V17" s="4"/>
-      <c r="W17" s="28"/>
+      <c r="W17" s="37"/>
     </row>
     <row r="18" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
@@ -2691,48 +2694,48 @@
       <c r="A19" s="8">
         <v>16</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="30" t="s">
         <v>6</v>
       </c>
       <c r="F19" s="26"/>
       <c r="G19" s="7">
         <v>16</v>
       </c>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="4"/>
-      <c r="K19" s="29" t="s">
+      <c r="K19" s="30" t="s">
         <v>6</v>
       </c>
       <c r="L19" s="26"/>
       <c r="M19" s="8">
         <v>16</v>
       </c>
-      <c r="N19" s="42" t="s">
+      <c r="N19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="4"/>
-      <c r="Q19" s="29" t="s">
+      <c r="Q19" s="30" t="s">
         <v>6</v>
       </c>
       <c r="R19" s="26"/>
       <c r="S19" s="7">
         <v>16</v>
       </c>
-      <c r="T19" s="42" t="s">
+      <c r="T19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="U19" s="1"/>
       <c r="V19" s="4"/>
-      <c r="W19" s="29" t="s">
+      <c r="W19" s="30" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2740,309 +2743,310 @@
       <c r="A20" s="8">
         <v>17</v>
       </c>
-      <c r="B20" s="42"/>
+      <c r="B20" s="28"/>
       <c r="C20" s="3"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="29"/>
+      <c r="E20" s="30"/>
       <c r="F20" s="26"/>
       <c r="G20" s="7">
         <v>17</v>
       </c>
-      <c r="H20" s="42"/>
+      <c r="H20" s="28"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-      <c r="K20" s="29"/>
+      <c r="K20" s="30"/>
       <c r="L20" s="26"/>
       <c r="M20" s="7">
         <v>17</v>
       </c>
-      <c r="N20" s="42"/>
+      <c r="N20" s="28"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="29"/>
+      <c r="Q20" s="30"/>
       <c r="R20" s="26"/>
       <c r="S20" s="7">
         <v>17</v>
       </c>
-      <c r="T20" s="42"/>
+      <c r="T20" s="28"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
-      <c r="W20" s="29"/>
+      <c r="W20" s="30"/>
     </row>
     <row r="21" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>18</v>
       </c>
-      <c r="B21" s="42"/>
+      <c r="B21" s="28"/>
       <c r="C21" s="3"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="29"/>
+      <c r="E21" s="30"/>
       <c r="F21" s="26"/>
       <c r="G21" s="7">
         <v>18</v>
       </c>
-      <c r="H21" s="42"/>
+      <c r="H21" s="28"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="29"/>
+      <c r="K21" s="30"/>
       <c r="L21" s="26"/>
       <c r="M21" s="7">
         <v>18</v>
       </c>
-      <c r="N21" s="42"/>
+      <c r="N21" s="28"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="29"/>
+      <c r="Q21" s="30"/>
       <c r="R21" s="26"/>
       <c r="S21" s="7">
         <v>18</v>
       </c>
-      <c r="T21" s="42"/>
+      <c r="T21" s="28"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
-      <c r="W21" s="29"/>
+      <c r="W21" s="30"/>
     </row>
     <row r="22" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>19</v>
       </c>
-      <c r="B22" s="42"/>
+      <c r="B22" s="28"/>
       <c r="C22" s="3"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="29"/>
+      <c r="E22" s="30"/>
       <c r="F22" s="26"/>
       <c r="G22" s="7">
         <v>19</v>
       </c>
-      <c r="H22" s="42"/>
+      <c r="H22" s="28"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-      <c r="K22" s="29"/>
+      <c r="K22" s="30"/>
       <c r="L22" s="26"/>
       <c r="M22" s="7">
         <v>19</v>
       </c>
-      <c r="N22" s="42"/>
+      <c r="N22" s="28"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
-      <c r="Q22" s="29"/>
+      <c r="Q22" s="30"/>
       <c r="R22" s="26"/>
       <c r="S22" s="7">
         <v>19</v>
       </c>
-      <c r="T22" s="42"/>
+      <c r="T22" s="28"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
-      <c r="W22" s="29"/>
+      <c r="W22" s="30"/>
     </row>
     <row r="23" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>20</v>
       </c>
-      <c r="B23" s="42"/>
+      <c r="B23" s="28"/>
       <c r="C23" s="3"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="29"/>
+      <c r="E23" s="30"/>
       <c r="F23" s="26"/>
       <c r="G23" s="7">
         <v>20</v>
       </c>
-      <c r="H23" s="42"/>
+      <c r="H23" s="28"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="29"/>
+      <c r="K23" s="30"/>
       <c r="L23" s="26"/>
       <c r="M23" s="7">
         <v>20</v>
       </c>
-      <c r="N23" s="42"/>
+      <c r="N23" s="28"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="29"/>
+      <c r="Q23" s="30"/>
       <c r="R23" s="26"/>
       <c r="S23" s="7">
         <v>20</v>
       </c>
-      <c r="T23" s="42"/>
+      <c r="T23" s="28"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
-      <c r="W23" s="29"/>
+      <c r="W23" s="30"/>
     </row>
     <row r="24" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>21</v>
       </c>
-      <c r="B24" s="42"/>
+      <c r="B24" s="28"/>
       <c r="C24" s="3"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="29"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="26"/>
       <c r="G24" s="7">
         <v>21</v>
       </c>
-      <c r="H24" s="42"/>
+      <c r="H24" s="28"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-      <c r="K24" s="29"/>
+      <c r="K24" s="30"/>
       <c r="L24" s="26"/>
       <c r="M24" s="7">
         <v>21</v>
       </c>
-      <c r="N24" s="42"/>
+      <c r="N24" s="28"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="29"/>
+      <c r="Q24" s="30"/>
       <c r="R24" s="26"/>
       <c r="S24" s="7">
         <v>21</v>
       </c>
-      <c r="T24" s="42"/>
+      <c r="T24" s="28"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
-      <c r="W24" s="29"/>
+      <c r="W24" s="30"/>
     </row>
     <row r="25" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>22</v>
       </c>
-      <c r="B25" s="42"/>
+      <c r="B25" s="28"/>
       <c r="C25" s="3"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="29"/>
+      <c r="E25" s="30"/>
       <c r="F25" s="26"/>
       <c r="G25" s="7">
         <v>22</v>
       </c>
-      <c r="H25" s="42"/>
+      <c r="H25" s="28"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="29"/>
+      <c r="K25" s="30"/>
       <c r="L25" s="26"/>
       <c r="M25" s="7">
         <v>22</v>
       </c>
-      <c r="N25" s="42"/>
+      <c r="N25" s="28"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="29"/>
+      <c r="Q25" s="30"/>
       <c r="R25" s="26"/>
       <c r="S25" s="7">
         <v>22</v>
       </c>
-      <c r="T25" s="42"/>
+      <c r="T25" s="28"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
-      <c r="W25" s="29"/>
+      <c r="W25" s="30"/>
     </row>
     <row r="26" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>23</v>
       </c>
-      <c r="B26" s="42"/>
+      <c r="B26" s="28"/>
       <c r="C26" s="3"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="29"/>
+      <c r="E26" s="30"/>
       <c r="F26" s="26"/>
       <c r="G26" s="7">
         <v>23</v>
       </c>
-      <c r="H26" s="42"/>
+      <c r="H26" s="28"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="29"/>
+      <c r="K26" s="30"/>
       <c r="L26" s="26"/>
       <c r="M26" s="7">
         <v>23</v>
       </c>
-      <c r="N26" s="42"/>
+      <c r="N26" s="28"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="29"/>
+      <c r="Q26" s="30"/>
       <c r="R26" s="26"/>
       <c r="S26" s="7">
         <v>23</v>
       </c>
-      <c r="T26" s="42"/>
+      <c r="T26" s="28"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
-      <c r="W26" s="29"/>
+      <c r="W26" s="30"/>
     </row>
     <row r="27" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>24</v>
       </c>
-      <c r="B27" s="42"/>
+      <c r="B27" s="28"/>
       <c r="C27" s="3"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="29"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="26"/>
       <c r="G27" s="7">
         <v>24</v>
       </c>
-      <c r="H27" s="42"/>
+      <c r="H27" s="28"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="29"/>
+      <c r="K27" s="30"/>
       <c r="L27" s="26"/>
       <c r="M27" s="7">
         <v>24</v>
       </c>
-      <c r="N27" s="42"/>
+      <c r="N27" s="28"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="29"/>
+      <c r="Q27" s="30"/>
       <c r="R27" s="26"/>
       <c r="S27" s="7">
         <v>24</v>
       </c>
-      <c r="T27" s="42"/>
+      <c r="T27" s="28"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
-      <c r="W27" s="29"/>
+      <c r="W27" s="30"/>
     </row>
     <row r="28" spans="1:23" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11">
         <v>25</v>
       </c>
-      <c r="B28" s="43"/>
+      <c r="B28" s="29"/>
       <c r="C28" s="12"/>
       <c r="D28" s="10"/>
-      <c r="E28" s="30"/>
+      <c r="E28" s="31"/>
       <c r="F28" s="27"/>
       <c r="G28" s="9">
         <v>25</v>
       </c>
-      <c r="H28" s="43"/>
+      <c r="H28" s="29"/>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
-      <c r="K28" s="30"/>
+      <c r="K28" s="31"/>
       <c r="L28" s="27"/>
       <c r="M28" s="9">
         <v>25</v>
       </c>
-      <c r="N28" s="43"/>
+      <c r="N28" s="29"/>
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
-      <c r="Q28" s="30"/>
+      <c r="Q28" s="31"/>
       <c r="R28" s="27"/>
       <c r="S28" s="9">
         <v>25</v>
       </c>
-      <c r="T28" s="43"/>
+      <c r="T28" s="29"/>
       <c r="U28" s="10"/>
       <c r="V28" s="10"/>
-      <c r="W28" s="30"/>
+      <c r="W28" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="T19:T28"/>
-    <mergeCell ref="W19:W28"/>
-    <mergeCell ref="B19:B28"/>
-    <mergeCell ref="E19:E28"/>
-    <mergeCell ref="H19:H28"/>
-    <mergeCell ref="K19:K28"/>
-    <mergeCell ref="N19:N28"/>
-    <mergeCell ref="Q19:Q28"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
     <mergeCell ref="T4:T9"/>
     <mergeCell ref="W4:W9"/>
     <mergeCell ref="B10:B17"/>
@@ -3059,18 +3063,17 @@
     <mergeCell ref="K4:K9"/>
     <mergeCell ref="N4:N9"/>
     <mergeCell ref="Q4:Q9"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="T19:T28"/>
+    <mergeCell ref="W19:W28"/>
+    <mergeCell ref="B19:B28"/>
+    <mergeCell ref="E19:E28"/>
+    <mergeCell ref="H19:H28"/>
+    <mergeCell ref="K19:K28"/>
+    <mergeCell ref="N19:N28"/>
+    <mergeCell ref="Q19:Q28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="75" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="60" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3106,71 +3109,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="22.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
-      <c r="U1" s="54"/>
-      <c r="V1" s="54"/>
-      <c r="W1" s="55"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="52"/>
     </row>
     <row r="2" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="31">
+      <c r="B2" s="42"/>
+      <c r="C2" s="43">
         <v>46113</v>
       </c>
-      <c r="D2" s="32"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="6"/>
       <c r="F2" s="22"/>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="34"/>
-      <c r="I2" s="31">
+      <c r="H2" s="46"/>
+      <c r="I2" s="43">
         <v>46113</v>
       </c>
-      <c r="J2" s="32"/>
+      <c r="J2" s="44"/>
       <c r="K2" s="6"/>
       <c r="L2" s="22"/>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="34"/>
-      <c r="O2" s="31">
+      <c r="N2" s="46"/>
+      <c r="O2" s="43">
         <v>46113</v>
       </c>
-      <c r="P2" s="32"/>
+      <c r="P2" s="44"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="22"/>
-      <c r="S2" s="33" t="s">
+      <c r="S2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="T2" s="34"/>
-      <c r="U2" s="31">
+      <c r="T2" s="46"/>
+      <c r="U2" s="43">
         <v>46113</v>
       </c>
-      <c r="V2" s="32"/>
+      <c r="V2" s="44"/>
       <c r="W2" s="6"/>
     </row>
     <row r="3" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3218,48 +3221,48 @@
       <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="24"/>
       <c r="G4" s="7">
         <v>1</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="39" t="s">
+      <c r="K4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="L4" s="24"/>
       <c r="M4" s="7">
         <v>1</v>
       </c>
-      <c r="N4" s="37" t="s">
+      <c r="N4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-      <c r="Q4" s="39" t="s">
+      <c r="Q4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="R4" s="24"/>
       <c r="S4" s="7">
         <v>1</v>
       </c>
-      <c r="T4" s="37" t="s">
+      <c r="T4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
-      <c r="W4" s="39" t="s">
+      <c r="W4" s="34" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3267,213 +3270,213 @@
       <c r="A5" s="8">
         <v>2</v>
       </c>
-      <c r="B5" s="38"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="3"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="40"/>
+      <c r="E5" s="35"/>
       <c r="F5" s="24"/>
       <c r="G5" s="7">
         <v>2</v>
       </c>
-      <c r="H5" s="38"/>
+      <c r="H5" s="33"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="40"/>
+      <c r="K5" s="35"/>
       <c r="L5" s="24"/>
       <c r="M5" s="7">
         <v>2</v>
       </c>
-      <c r="N5" s="38"/>
+      <c r="N5" s="33"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
-      <c r="Q5" s="40"/>
+      <c r="Q5" s="35"/>
       <c r="R5" s="24"/>
       <c r="S5" s="7">
         <v>2</v>
       </c>
-      <c r="T5" s="38"/>
+      <c r="T5" s="33"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
-      <c r="W5" s="40"/>
+      <c r="W5" s="35"/>
     </row>
     <row r="6" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>3</v>
       </c>
-      <c r="B6" s="38"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="3"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="40"/>
+      <c r="E6" s="35"/>
       <c r="F6" s="24"/>
       <c r="G6" s="7">
         <v>3</v>
       </c>
-      <c r="H6" s="38"/>
+      <c r="H6" s="33"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="40"/>
+      <c r="K6" s="35"/>
       <c r="L6" s="24"/>
       <c r="M6" s="7">
         <v>3</v>
       </c>
-      <c r="N6" s="38"/>
+      <c r="N6" s="33"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="40"/>
+      <c r="Q6" s="35"/>
       <c r="R6" s="24"/>
       <c r="S6" s="7">
         <v>3</v>
       </c>
-      <c r="T6" s="38"/>
+      <c r="T6" s="33"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
-      <c r="W6" s="40"/>
+      <c r="W6" s="35"/>
     </row>
     <row r="7" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>4</v>
       </c>
-      <c r="B7" s="38"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="3"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="40"/>
+      <c r="E7" s="35"/>
       <c r="F7" s="24"/>
       <c r="G7" s="7">
         <v>4</v>
       </c>
-      <c r="H7" s="38"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="40"/>
+      <c r="K7" s="35"/>
       <c r="L7" s="24"/>
       <c r="M7" s="7">
         <v>4</v>
       </c>
-      <c r="N7" s="38"/>
+      <c r="N7" s="33"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="40"/>
+      <c r="Q7" s="35"/>
       <c r="R7" s="24"/>
       <c r="S7" s="7">
         <v>4</v>
       </c>
-      <c r="T7" s="38"/>
+      <c r="T7" s="33"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
-      <c r="W7" s="40"/>
+      <c r="W7" s="35"/>
     </row>
     <row r="8" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>5</v>
       </c>
-      <c r="B8" s="38"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="3"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="40"/>
+      <c r="E8" s="35"/>
       <c r="F8" s="24"/>
       <c r="G8" s="7">
         <v>5</v>
       </c>
-      <c r="H8" s="38"/>
+      <c r="H8" s="33"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="40"/>
+      <c r="K8" s="35"/>
       <c r="L8" s="24"/>
       <c r="M8" s="7">
         <v>5</v>
       </c>
-      <c r="N8" s="38"/>
+      <c r="N8" s="33"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
-      <c r="Q8" s="40"/>
+      <c r="Q8" s="35"/>
       <c r="R8" s="24"/>
       <c r="S8" s="7">
         <v>5</v>
       </c>
-      <c r="T8" s="38"/>
+      <c r="T8" s="33"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
-      <c r="W8" s="40"/>
+      <c r="W8" s="35"/>
     </row>
     <row r="9" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>6</v>
       </c>
-      <c r="B9" s="38"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="3"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="40"/>
+      <c r="E9" s="35"/>
       <c r="F9" s="24"/>
       <c r="G9" s="7">
         <v>6</v>
       </c>
-      <c r="H9" s="38"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="40"/>
+      <c r="K9" s="35"/>
       <c r="L9" s="24"/>
       <c r="M9" s="7">
         <v>6</v>
       </c>
-      <c r="N9" s="38"/>
+      <c r="N9" s="33"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-      <c r="Q9" s="40"/>
+      <c r="Q9" s="35"/>
       <c r="R9" s="24"/>
       <c r="S9" s="7">
         <v>6</v>
       </c>
-      <c r="T9" s="38"/>
+      <c r="T9" s="33"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
-      <c r="W9" s="40"/>
+      <c r="W9" s="35"/>
     </row>
     <row r="10" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>7</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="37" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="25"/>
       <c r="G10" s="7">
         <v>7</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="H10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="28" t="s">
+      <c r="K10" s="37" t="s">
         <v>4</v>
       </c>
       <c r="L10" s="25"/>
       <c r="M10" s="8">
         <v>7</v>
       </c>
-      <c r="N10" s="41" t="s">
+      <c r="N10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="4"/>
-      <c r="Q10" s="28" t="s">
+      <c r="Q10" s="37" t="s">
         <v>4</v>
       </c>
       <c r="R10" s="25"/>
       <c r="S10" s="7">
         <v>7</v>
       </c>
-      <c r="T10" s="41" t="s">
+      <c r="T10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="U10" s="1"/>
       <c r="V10" s="4"/>
-      <c r="W10" s="28" t="s">
+      <c r="W10" s="37" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3481,232 +3484,232 @@
       <c r="A11" s="8">
         <v>8</v>
       </c>
-      <c r="B11" s="41"/>
+      <c r="B11" s="36"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="28"/>
+      <c r="E11" s="37"/>
       <c r="F11" s="25"/>
       <c r="G11" s="7">
         <v>8</v>
       </c>
-      <c r="H11" s="41"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="1"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="28"/>
+      <c r="K11" s="37"/>
       <c r="L11" s="25"/>
       <c r="M11" s="8">
         <v>8</v>
       </c>
-      <c r="N11" s="41"/>
+      <c r="N11" s="36"/>
       <c r="O11" s="3"/>
       <c r="P11" s="4"/>
-      <c r="Q11" s="28"/>
+      <c r="Q11" s="37"/>
       <c r="R11" s="25"/>
       <c r="S11" s="7">
         <v>8</v>
       </c>
-      <c r="T11" s="41"/>
+      <c r="T11" s="36"/>
       <c r="U11" s="1"/>
       <c r="V11" s="4"/>
-      <c r="W11" s="28"/>
+      <c r="W11" s="37"/>
     </row>
     <row r="12" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>9</v>
       </c>
-      <c r="B12" s="41"/>
+      <c r="B12" s="36"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="28"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="25"/>
       <c r="G12" s="7">
         <v>9</v>
       </c>
-      <c r="H12" s="41"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="1"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="28"/>
+      <c r="K12" s="37"/>
       <c r="L12" s="25"/>
       <c r="M12" s="8">
         <v>9</v>
       </c>
-      <c r="N12" s="41"/>
+      <c r="N12" s="36"/>
       <c r="O12" s="3"/>
       <c r="P12" s="4"/>
-      <c r="Q12" s="28"/>
+      <c r="Q12" s="37"/>
       <c r="R12" s="25"/>
       <c r="S12" s="7">
         <v>9</v>
       </c>
-      <c r="T12" s="41"/>
+      <c r="T12" s="36"/>
       <c r="U12" s="1"/>
       <c r="V12" s="4"/>
-      <c r="W12" s="28"/>
+      <c r="W12" s="37"/>
     </row>
     <row r="13" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>10</v>
       </c>
-      <c r="B13" s="41"/>
+      <c r="B13" s="36"/>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="28"/>
+      <c r="E13" s="37"/>
       <c r="F13" s="25"/>
       <c r="G13" s="7">
         <v>10</v>
       </c>
-      <c r="H13" s="41"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="1"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="28"/>
+      <c r="K13" s="37"/>
       <c r="L13" s="25"/>
       <c r="M13" s="8">
         <v>10</v>
       </c>
-      <c r="N13" s="41"/>
+      <c r="N13" s="36"/>
       <c r="O13" s="3"/>
       <c r="P13" s="4"/>
-      <c r="Q13" s="28"/>
+      <c r="Q13" s="37"/>
       <c r="R13" s="25"/>
       <c r="S13" s="7">
         <v>10</v>
       </c>
-      <c r="T13" s="41"/>
+      <c r="T13" s="36"/>
       <c r="U13" s="1"/>
       <c r="V13" s="4"/>
-      <c r="W13" s="28"/>
+      <c r="W13" s="37"/>
     </row>
     <row r="14" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>11</v>
       </c>
-      <c r="B14" s="41"/>
+      <c r="B14" s="36"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="28"/>
+      <c r="E14" s="37"/>
       <c r="F14" s="25"/>
       <c r="G14" s="7">
         <v>11</v>
       </c>
-      <c r="H14" s="41"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="1"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="28"/>
+      <c r="K14" s="37"/>
       <c r="L14" s="25"/>
       <c r="M14" s="8">
         <v>11</v>
       </c>
-      <c r="N14" s="41"/>
+      <c r="N14" s="36"/>
       <c r="O14" s="3"/>
       <c r="P14" s="4"/>
-      <c r="Q14" s="28"/>
+      <c r="Q14" s="37"/>
       <c r="R14" s="25"/>
       <c r="S14" s="7">
         <v>11</v>
       </c>
-      <c r="T14" s="41"/>
+      <c r="T14" s="36"/>
       <c r="U14" s="1"/>
       <c r="V14" s="4"/>
-      <c r="W14" s="28"/>
+      <c r="W14" s="37"/>
     </row>
     <row r="15" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>12</v>
       </c>
-      <c r="B15" s="41"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="28"/>
+      <c r="E15" s="37"/>
       <c r="F15" s="25"/>
       <c r="G15" s="7">
         <v>12</v>
       </c>
-      <c r="H15" s="41"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="1"/>
       <c r="J15" s="4"/>
-      <c r="K15" s="28"/>
+      <c r="K15" s="37"/>
       <c r="L15" s="25"/>
       <c r="M15" s="8">
         <v>12</v>
       </c>
-      <c r="N15" s="41"/>
+      <c r="N15" s="36"/>
       <c r="O15" s="3"/>
       <c r="P15" s="4"/>
-      <c r="Q15" s="28"/>
+      <c r="Q15" s="37"/>
       <c r="R15" s="25"/>
       <c r="S15" s="7">
         <v>12</v>
       </c>
-      <c r="T15" s="41"/>
+      <c r="T15" s="36"/>
       <c r="U15" s="1"/>
       <c r="V15" s="4"/>
-      <c r="W15" s="28"/>
+      <c r="W15" s="37"/>
     </row>
     <row r="16" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>13</v>
       </c>
-      <c r="B16" s="41"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="3"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="28"/>
+      <c r="E16" s="37"/>
       <c r="F16" s="25"/>
       <c r="G16" s="7">
         <v>13</v>
       </c>
-      <c r="H16" s="41"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="1"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="28"/>
+      <c r="K16" s="37"/>
       <c r="L16" s="25"/>
       <c r="M16" s="8">
         <v>13</v>
       </c>
-      <c r="N16" s="41"/>
+      <c r="N16" s="36"/>
       <c r="O16" s="3"/>
       <c r="P16" s="4"/>
-      <c r="Q16" s="28"/>
+      <c r="Q16" s="37"/>
       <c r="R16" s="25"/>
       <c r="S16" s="7">
         <v>13</v>
       </c>
-      <c r="T16" s="41"/>
+      <c r="T16" s="36"/>
       <c r="U16" s="1"/>
       <c r="V16" s="4"/>
-      <c r="W16" s="28"/>
+      <c r="W16" s="37"/>
     </row>
     <row r="17" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>14</v>
       </c>
-      <c r="B17" s="41"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="28"/>
+      <c r="E17" s="37"/>
       <c r="F17" s="25"/>
       <c r="G17" s="7">
         <v>14</v>
       </c>
-      <c r="H17" s="41"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="1"/>
       <c r="J17" s="4"/>
-      <c r="K17" s="28"/>
+      <c r="K17" s="37"/>
       <c r="L17" s="25"/>
       <c r="M17" s="8">
         <v>14</v>
       </c>
-      <c r="N17" s="41"/>
+      <c r="N17" s="36"/>
       <c r="O17" s="3"/>
       <c r="P17" s="4"/>
-      <c r="Q17" s="28"/>
+      <c r="Q17" s="37"/>
       <c r="R17" s="25"/>
       <c r="S17" s="7">
         <v>14</v>
       </c>
-      <c r="T17" s="41"/>
+      <c r="T17" s="36"/>
       <c r="U17" s="1"/>
       <c r="V17" s="4"/>
-      <c r="W17" s="28"/>
+      <c r="W17" s="37"/>
     </row>
     <row r="18" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
@@ -3761,48 +3764,48 @@
       <c r="A19" s="8">
         <v>16</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="30" t="s">
         <v>6</v>
       </c>
       <c r="F19" s="26"/>
       <c r="G19" s="7">
         <v>16</v>
       </c>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="4"/>
-      <c r="K19" s="29" t="s">
+      <c r="K19" s="30" t="s">
         <v>6</v>
       </c>
       <c r="L19" s="26"/>
       <c r="M19" s="8">
         <v>16</v>
       </c>
-      <c r="N19" s="42" t="s">
+      <c r="N19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="4"/>
-      <c r="Q19" s="29" t="s">
+      <c r="Q19" s="30" t="s">
         <v>6</v>
       </c>
       <c r="R19" s="26"/>
       <c r="S19" s="7">
         <v>16</v>
       </c>
-      <c r="T19" s="42" t="s">
+      <c r="T19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="U19" s="1"/>
       <c r="V19" s="4"/>
-      <c r="W19" s="29" t="s">
+      <c r="W19" s="30" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3810,309 +3813,310 @@
       <c r="A20" s="8">
         <v>17</v>
       </c>
-      <c r="B20" s="42"/>
+      <c r="B20" s="28"/>
       <c r="C20" s="3"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="29"/>
+      <c r="E20" s="30"/>
       <c r="F20" s="26"/>
       <c r="G20" s="7">
         <v>17</v>
       </c>
-      <c r="H20" s="42"/>
+      <c r="H20" s="28"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-      <c r="K20" s="29"/>
+      <c r="K20" s="30"/>
       <c r="L20" s="26"/>
       <c r="M20" s="7">
         <v>17</v>
       </c>
-      <c r="N20" s="42"/>
+      <c r="N20" s="28"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="29"/>
+      <c r="Q20" s="30"/>
       <c r="R20" s="26"/>
       <c r="S20" s="7">
         <v>17</v>
       </c>
-      <c r="T20" s="42"/>
+      <c r="T20" s="28"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
-      <c r="W20" s="29"/>
+      <c r="W20" s="30"/>
     </row>
     <row r="21" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>18</v>
       </c>
-      <c r="B21" s="42"/>
+      <c r="B21" s="28"/>
       <c r="C21" s="3"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="29"/>
+      <c r="E21" s="30"/>
       <c r="F21" s="26"/>
       <c r="G21" s="7">
         <v>18</v>
       </c>
-      <c r="H21" s="42"/>
+      <c r="H21" s="28"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="29"/>
+      <c r="K21" s="30"/>
       <c r="L21" s="26"/>
       <c r="M21" s="7">
         <v>18</v>
       </c>
-      <c r="N21" s="42"/>
+      <c r="N21" s="28"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="29"/>
+      <c r="Q21" s="30"/>
       <c r="R21" s="26"/>
       <c r="S21" s="7">
         <v>18</v>
       </c>
-      <c r="T21" s="42"/>
+      <c r="T21" s="28"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
-      <c r="W21" s="29"/>
+      <c r="W21" s="30"/>
     </row>
     <row r="22" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>19</v>
       </c>
-      <c r="B22" s="42"/>
+      <c r="B22" s="28"/>
       <c r="C22" s="3"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="29"/>
+      <c r="E22" s="30"/>
       <c r="F22" s="26"/>
       <c r="G22" s="7">
         <v>19</v>
       </c>
-      <c r="H22" s="42"/>
+      <c r="H22" s="28"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-      <c r="K22" s="29"/>
+      <c r="K22" s="30"/>
       <c r="L22" s="26"/>
       <c r="M22" s="7">
         <v>19</v>
       </c>
-      <c r="N22" s="42"/>
+      <c r="N22" s="28"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
-      <c r="Q22" s="29"/>
+      <c r="Q22" s="30"/>
       <c r="R22" s="26"/>
       <c r="S22" s="7">
         <v>19</v>
       </c>
-      <c r="T22" s="42"/>
+      <c r="T22" s="28"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
-      <c r="W22" s="29"/>
+      <c r="W22" s="30"/>
     </row>
     <row r="23" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>20</v>
       </c>
-      <c r="B23" s="42"/>
+      <c r="B23" s="28"/>
       <c r="C23" s="3"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="29"/>
+      <c r="E23" s="30"/>
       <c r="F23" s="26"/>
       <c r="G23" s="7">
         <v>20</v>
       </c>
-      <c r="H23" s="42"/>
+      <c r="H23" s="28"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="29"/>
+      <c r="K23" s="30"/>
       <c r="L23" s="26"/>
       <c r="M23" s="7">
         <v>20</v>
       </c>
-      <c r="N23" s="42"/>
+      <c r="N23" s="28"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="29"/>
+      <c r="Q23" s="30"/>
       <c r="R23" s="26"/>
       <c r="S23" s="7">
         <v>20</v>
       </c>
-      <c r="T23" s="42"/>
+      <c r="T23" s="28"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
-      <c r="W23" s="29"/>
+      <c r="W23" s="30"/>
     </row>
     <row r="24" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>21</v>
       </c>
-      <c r="B24" s="42"/>
+      <c r="B24" s="28"/>
       <c r="C24" s="3"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="29"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="26"/>
       <c r="G24" s="7">
         <v>21</v>
       </c>
-      <c r="H24" s="42"/>
+      <c r="H24" s="28"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-      <c r="K24" s="29"/>
+      <c r="K24" s="30"/>
       <c r="L24" s="26"/>
       <c r="M24" s="7">
         <v>21</v>
       </c>
-      <c r="N24" s="42"/>
+      <c r="N24" s="28"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="29"/>
+      <c r="Q24" s="30"/>
       <c r="R24" s="26"/>
       <c r="S24" s="7">
         <v>21</v>
       </c>
-      <c r="T24" s="42"/>
+      <c r="T24" s="28"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
-      <c r="W24" s="29"/>
+      <c r="W24" s="30"/>
     </row>
     <row r="25" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>22</v>
       </c>
-      <c r="B25" s="42"/>
+      <c r="B25" s="28"/>
       <c r="C25" s="3"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="29"/>
+      <c r="E25" s="30"/>
       <c r="F25" s="26"/>
       <c r="G25" s="7">
         <v>22</v>
       </c>
-      <c r="H25" s="42"/>
+      <c r="H25" s="28"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="29"/>
+      <c r="K25" s="30"/>
       <c r="L25" s="26"/>
       <c r="M25" s="7">
         <v>22</v>
       </c>
-      <c r="N25" s="42"/>
+      <c r="N25" s="28"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="29"/>
+      <c r="Q25" s="30"/>
       <c r="R25" s="26"/>
       <c r="S25" s="7">
         <v>22</v>
       </c>
-      <c r="T25" s="42"/>
+      <c r="T25" s="28"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
-      <c r="W25" s="29"/>
+      <c r="W25" s="30"/>
     </row>
     <row r="26" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>23</v>
       </c>
-      <c r="B26" s="42"/>
+      <c r="B26" s="28"/>
       <c r="C26" s="3"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="29"/>
+      <c r="E26" s="30"/>
       <c r="F26" s="26"/>
       <c r="G26" s="7">
         <v>23</v>
       </c>
-      <c r="H26" s="42"/>
+      <c r="H26" s="28"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="29"/>
+      <c r="K26" s="30"/>
       <c r="L26" s="26"/>
       <c r="M26" s="7">
         <v>23</v>
       </c>
-      <c r="N26" s="42"/>
+      <c r="N26" s="28"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="29"/>
+      <c r="Q26" s="30"/>
       <c r="R26" s="26"/>
       <c r="S26" s="7">
         <v>23</v>
       </c>
-      <c r="T26" s="42"/>
+      <c r="T26" s="28"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
-      <c r="W26" s="29"/>
+      <c r="W26" s="30"/>
     </row>
     <row r="27" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>24</v>
       </c>
-      <c r="B27" s="42"/>
+      <c r="B27" s="28"/>
       <c r="C27" s="3"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="29"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="26"/>
       <c r="G27" s="7">
         <v>24</v>
       </c>
-      <c r="H27" s="42"/>
+      <c r="H27" s="28"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="29"/>
+      <c r="K27" s="30"/>
       <c r="L27" s="26"/>
       <c r="M27" s="7">
         <v>24</v>
       </c>
-      <c r="N27" s="42"/>
+      <c r="N27" s="28"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="29"/>
+      <c r="Q27" s="30"/>
       <c r="R27" s="26"/>
       <c r="S27" s="7">
         <v>24</v>
       </c>
-      <c r="T27" s="42"/>
+      <c r="T27" s="28"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
-      <c r="W27" s="29"/>
+      <c r="W27" s="30"/>
     </row>
     <row r="28" spans="1:23" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11">
         <v>25</v>
       </c>
-      <c r="B28" s="43"/>
+      <c r="B28" s="29"/>
       <c r="C28" s="12"/>
       <c r="D28" s="10"/>
-      <c r="E28" s="30"/>
+      <c r="E28" s="31"/>
       <c r="F28" s="27"/>
       <c r="G28" s="9">
         <v>25</v>
       </c>
-      <c r="H28" s="43"/>
+      <c r="H28" s="29"/>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
-      <c r="K28" s="30"/>
+      <c r="K28" s="31"/>
       <c r="L28" s="27"/>
       <c r="M28" s="9">
         <v>25</v>
       </c>
-      <c r="N28" s="43"/>
+      <c r="N28" s="29"/>
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
-      <c r="Q28" s="30"/>
+      <c r="Q28" s="31"/>
       <c r="R28" s="27"/>
       <c r="S28" s="9">
         <v>25</v>
       </c>
-      <c r="T28" s="43"/>
+      <c r="T28" s="29"/>
       <c r="U28" s="10"/>
       <c r="V28" s="10"/>
-      <c r="W28" s="30"/>
+      <c r="W28" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="T19:T28"/>
-    <mergeCell ref="W19:W28"/>
-    <mergeCell ref="B19:B28"/>
-    <mergeCell ref="E19:E28"/>
-    <mergeCell ref="H19:H28"/>
-    <mergeCell ref="K19:K28"/>
-    <mergeCell ref="N19:N28"/>
-    <mergeCell ref="Q19:Q28"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
     <mergeCell ref="T4:T9"/>
     <mergeCell ref="W4:W9"/>
     <mergeCell ref="B10:B17"/>
@@ -4129,18 +4133,17 @@
     <mergeCell ref="K4:K9"/>
     <mergeCell ref="N4:N9"/>
     <mergeCell ref="Q4:Q9"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="T19:T28"/>
+    <mergeCell ref="W19:W28"/>
+    <mergeCell ref="B19:B28"/>
+    <mergeCell ref="E19:E28"/>
+    <mergeCell ref="H19:H28"/>
+    <mergeCell ref="K19:K28"/>
+    <mergeCell ref="N19:N28"/>
+    <mergeCell ref="Q19:Q28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="75" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="60" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4176,71 +4179,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="22.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="46"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="55"/>
     </row>
     <row r="2" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="31">
+      <c r="B2" s="42"/>
+      <c r="C2" s="43">
         <v>46113</v>
       </c>
-      <c r="D2" s="32"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="6"/>
       <c r="F2" s="22"/>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="34"/>
-      <c r="I2" s="31">
+      <c r="H2" s="46"/>
+      <c r="I2" s="43">
         <v>46113</v>
       </c>
-      <c r="J2" s="32"/>
+      <c r="J2" s="44"/>
       <c r="K2" s="6"/>
       <c r="L2" s="22"/>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="34"/>
-      <c r="O2" s="31">
+      <c r="N2" s="46"/>
+      <c r="O2" s="43">
         <v>46113</v>
       </c>
-      <c r="P2" s="32"/>
+      <c r="P2" s="44"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="22"/>
-      <c r="S2" s="33" t="s">
+      <c r="S2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="T2" s="34"/>
-      <c r="U2" s="31">
+      <c r="T2" s="46"/>
+      <c r="U2" s="43">
         <v>46113</v>
       </c>
-      <c r="V2" s="32"/>
+      <c r="V2" s="44"/>
       <c r="W2" s="6"/>
     </row>
     <row r="3" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4288,48 +4291,48 @@
       <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="24"/>
       <c r="G4" s="7">
         <v>1</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="39" t="s">
+      <c r="K4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="L4" s="24"/>
       <c r="M4" s="7">
         <v>1</v>
       </c>
-      <c r="N4" s="37" t="s">
+      <c r="N4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-      <c r="Q4" s="39" t="s">
+      <c r="Q4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="R4" s="24"/>
       <c r="S4" s="7">
         <v>1</v>
       </c>
-      <c r="T4" s="37" t="s">
+      <c r="T4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
-      <c r="W4" s="39" t="s">
+      <c r="W4" s="34" t="s">
         <v>3</v>
       </c>
     </row>
@@ -4337,213 +4340,213 @@
       <c r="A5" s="8">
         <v>2</v>
       </c>
-      <c r="B5" s="38"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="3"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="40"/>
+      <c r="E5" s="35"/>
       <c r="F5" s="24"/>
       <c r="G5" s="7">
         <v>2</v>
       </c>
-      <c r="H5" s="38"/>
+      <c r="H5" s="33"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="40"/>
+      <c r="K5" s="35"/>
       <c r="L5" s="24"/>
       <c r="M5" s="7">
         <v>2</v>
       </c>
-      <c r="N5" s="38"/>
+      <c r="N5" s="33"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
-      <c r="Q5" s="40"/>
+      <c r="Q5" s="35"/>
       <c r="R5" s="24"/>
       <c r="S5" s="7">
         <v>2</v>
       </c>
-      <c r="T5" s="38"/>
+      <c r="T5" s="33"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
-      <c r="W5" s="40"/>
+      <c r="W5" s="35"/>
     </row>
     <row r="6" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>3</v>
       </c>
-      <c r="B6" s="38"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="3"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="40"/>
+      <c r="E6" s="35"/>
       <c r="F6" s="24"/>
       <c r="G6" s="7">
         <v>3</v>
       </c>
-      <c r="H6" s="38"/>
+      <c r="H6" s="33"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="40"/>
+      <c r="K6" s="35"/>
       <c r="L6" s="24"/>
       <c r="M6" s="7">
         <v>3</v>
       </c>
-      <c r="N6" s="38"/>
+      <c r="N6" s="33"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="40"/>
+      <c r="Q6" s="35"/>
       <c r="R6" s="24"/>
       <c r="S6" s="7">
         <v>3</v>
       </c>
-      <c r="T6" s="38"/>
+      <c r="T6" s="33"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
-      <c r="W6" s="40"/>
+      <c r="W6" s="35"/>
     </row>
     <row r="7" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>4</v>
       </c>
-      <c r="B7" s="38"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="3"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="40"/>
+      <c r="E7" s="35"/>
       <c r="F7" s="24"/>
       <c r="G7" s="7">
         <v>4</v>
       </c>
-      <c r="H7" s="38"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="40"/>
+      <c r="K7" s="35"/>
       <c r="L7" s="24"/>
       <c r="M7" s="7">
         <v>4</v>
       </c>
-      <c r="N7" s="38"/>
+      <c r="N7" s="33"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="40"/>
+      <c r="Q7" s="35"/>
       <c r="R7" s="24"/>
       <c r="S7" s="7">
         <v>4</v>
       </c>
-      <c r="T7" s="38"/>
+      <c r="T7" s="33"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
-      <c r="W7" s="40"/>
+      <c r="W7" s="35"/>
     </row>
     <row r="8" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>5</v>
       </c>
-      <c r="B8" s="38"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="3"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="40"/>
+      <c r="E8" s="35"/>
       <c r="F8" s="24"/>
       <c r="G8" s="7">
         <v>5</v>
       </c>
-      <c r="H8" s="38"/>
+      <c r="H8" s="33"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="40"/>
+      <c r="K8" s="35"/>
       <c r="L8" s="24"/>
       <c r="M8" s="7">
         <v>5</v>
       </c>
-      <c r="N8" s="38"/>
+      <c r="N8" s="33"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
-      <c r="Q8" s="40"/>
+      <c r="Q8" s="35"/>
       <c r="R8" s="24"/>
       <c r="S8" s="7">
         <v>5</v>
       </c>
-      <c r="T8" s="38"/>
+      <c r="T8" s="33"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
-      <c r="W8" s="40"/>
+      <c r="W8" s="35"/>
     </row>
     <row r="9" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>6</v>
       </c>
-      <c r="B9" s="38"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="3"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="40"/>
+      <c r="E9" s="35"/>
       <c r="F9" s="24"/>
       <c r="G9" s="7">
         <v>6</v>
       </c>
-      <c r="H9" s="38"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="40"/>
+      <c r="K9" s="35"/>
       <c r="L9" s="24"/>
       <c r="M9" s="7">
         <v>6</v>
       </c>
-      <c r="N9" s="38"/>
+      <c r="N9" s="33"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-      <c r="Q9" s="40"/>
+      <c r="Q9" s="35"/>
       <c r="R9" s="24"/>
       <c r="S9" s="7">
         <v>6</v>
       </c>
-      <c r="T9" s="38"/>
+      <c r="T9" s="33"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
-      <c r="W9" s="40"/>
+      <c r="W9" s="35"/>
     </row>
     <row r="10" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>7</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="37" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="25"/>
       <c r="G10" s="7">
         <v>7</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="H10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="28" t="s">
+      <c r="K10" s="37" t="s">
         <v>4</v>
       </c>
       <c r="L10" s="25"/>
       <c r="M10" s="8">
         <v>7</v>
       </c>
-      <c r="N10" s="41" t="s">
+      <c r="N10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="4"/>
-      <c r="Q10" s="28" t="s">
+      <c r="Q10" s="37" t="s">
         <v>4</v>
       </c>
       <c r="R10" s="25"/>
       <c r="S10" s="7">
         <v>7</v>
       </c>
-      <c r="T10" s="41" t="s">
+      <c r="T10" s="36" t="s">
         <v>4</v>
       </c>
       <c r="U10" s="1"/>
       <c r="V10" s="4"/>
-      <c r="W10" s="28" t="s">
+      <c r="W10" s="37" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4551,232 +4554,232 @@
       <c r="A11" s="8">
         <v>8</v>
       </c>
-      <c r="B11" s="41"/>
+      <c r="B11" s="36"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="28"/>
+      <c r="E11" s="37"/>
       <c r="F11" s="25"/>
       <c r="G11" s="7">
         <v>8</v>
       </c>
-      <c r="H11" s="41"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="1"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="28"/>
+      <c r="K11" s="37"/>
       <c r="L11" s="25"/>
       <c r="M11" s="8">
         <v>8</v>
       </c>
-      <c r="N11" s="41"/>
+      <c r="N11" s="36"/>
       <c r="O11" s="3"/>
       <c r="P11" s="4"/>
-      <c r="Q11" s="28"/>
+      <c r="Q11" s="37"/>
       <c r="R11" s="25"/>
       <c r="S11" s="7">
         <v>8</v>
       </c>
-      <c r="T11" s="41"/>
+      <c r="T11" s="36"/>
       <c r="U11" s="1"/>
       <c r="V11" s="4"/>
-      <c r="W11" s="28"/>
+      <c r="W11" s="37"/>
     </row>
     <row r="12" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>9</v>
       </c>
-      <c r="B12" s="41"/>
+      <c r="B12" s="36"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="28"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="25"/>
       <c r="G12" s="7">
         <v>9</v>
       </c>
-      <c r="H12" s="41"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="1"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="28"/>
+      <c r="K12" s="37"/>
       <c r="L12" s="25"/>
       <c r="M12" s="8">
         <v>9</v>
       </c>
-      <c r="N12" s="41"/>
+      <c r="N12" s="36"/>
       <c r="O12" s="3"/>
       <c r="P12" s="4"/>
-      <c r="Q12" s="28"/>
+      <c r="Q12" s="37"/>
       <c r="R12" s="25"/>
       <c r="S12" s="7">
         <v>9</v>
       </c>
-      <c r="T12" s="41"/>
+      <c r="T12" s="36"/>
       <c r="U12" s="1"/>
       <c r="V12" s="4"/>
-      <c r="W12" s="28"/>
+      <c r="W12" s="37"/>
     </row>
     <row r="13" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>10</v>
       </c>
-      <c r="B13" s="41"/>
+      <c r="B13" s="36"/>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="28"/>
+      <c r="E13" s="37"/>
       <c r="F13" s="25"/>
       <c r="G13" s="7">
         <v>10</v>
       </c>
-      <c r="H13" s="41"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="1"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="28"/>
+      <c r="K13" s="37"/>
       <c r="L13" s="25"/>
       <c r="M13" s="8">
         <v>10</v>
       </c>
-      <c r="N13" s="41"/>
+      <c r="N13" s="36"/>
       <c r="O13" s="3"/>
       <c r="P13" s="4"/>
-      <c r="Q13" s="28"/>
+      <c r="Q13" s="37"/>
       <c r="R13" s="25"/>
       <c r="S13" s="7">
         <v>10</v>
       </c>
-      <c r="T13" s="41"/>
+      <c r="T13" s="36"/>
       <c r="U13" s="1"/>
       <c r="V13" s="4"/>
-      <c r="W13" s="28"/>
+      <c r="W13" s="37"/>
     </row>
     <row r="14" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>11</v>
       </c>
-      <c r="B14" s="41"/>
+      <c r="B14" s="36"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="28"/>
+      <c r="E14" s="37"/>
       <c r="F14" s="25"/>
       <c r="G14" s="7">
         <v>11</v>
       </c>
-      <c r="H14" s="41"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="1"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="28"/>
+      <c r="K14" s="37"/>
       <c r="L14" s="25"/>
       <c r="M14" s="8">
         <v>11</v>
       </c>
-      <c r="N14" s="41"/>
+      <c r="N14" s="36"/>
       <c r="O14" s="3"/>
       <c r="P14" s="4"/>
-      <c r="Q14" s="28"/>
+      <c r="Q14" s="37"/>
       <c r="R14" s="25"/>
       <c r="S14" s="7">
         <v>11</v>
       </c>
-      <c r="T14" s="41"/>
+      <c r="T14" s="36"/>
       <c r="U14" s="1"/>
       <c r="V14" s="4"/>
-      <c r="W14" s="28"/>
+      <c r="W14" s="37"/>
     </row>
     <row r="15" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>12</v>
       </c>
-      <c r="B15" s="41"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="28"/>
+      <c r="E15" s="37"/>
       <c r="F15" s="25"/>
       <c r="G15" s="7">
         <v>12</v>
       </c>
-      <c r="H15" s="41"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="1"/>
       <c r="J15" s="4"/>
-      <c r="K15" s="28"/>
+      <c r="K15" s="37"/>
       <c r="L15" s="25"/>
       <c r="M15" s="8">
         <v>12</v>
       </c>
-      <c r="N15" s="41"/>
+      <c r="N15" s="36"/>
       <c r="O15" s="3"/>
       <c r="P15" s="4"/>
-      <c r="Q15" s="28"/>
+      <c r="Q15" s="37"/>
       <c r="R15" s="25"/>
       <c r="S15" s="7">
         <v>12</v>
       </c>
-      <c r="T15" s="41"/>
+      <c r="T15" s="36"/>
       <c r="U15" s="1"/>
       <c r="V15" s="4"/>
-      <c r="W15" s="28"/>
+      <c r="W15" s="37"/>
     </row>
     <row r="16" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>13</v>
       </c>
-      <c r="B16" s="41"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="3"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="28"/>
+      <c r="E16" s="37"/>
       <c r="F16" s="25"/>
       <c r="G16" s="7">
         <v>13</v>
       </c>
-      <c r="H16" s="41"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="1"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="28"/>
+      <c r="K16" s="37"/>
       <c r="L16" s="25"/>
       <c r="M16" s="8">
         <v>13</v>
       </c>
-      <c r="N16" s="41"/>
+      <c r="N16" s="36"/>
       <c r="O16" s="3"/>
       <c r="P16" s="4"/>
-      <c r="Q16" s="28"/>
+      <c r="Q16" s="37"/>
       <c r="R16" s="25"/>
       <c r="S16" s="7">
         <v>13</v>
       </c>
-      <c r="T16" s="41"/>
+      <c r="T16" s="36"/>
       <c r="U16" s="1"/>
       <c r="V16" s="4"/>
-      <c r="W16" s="28"/>
+      <c r="W16" s="37"/>
     </row>
     <row r="17" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>14</v>
       </c>
-      <c r="B17" s="41"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="28"/>
+      <c r="E17" s="37"/>
       <c r="F17" s="25"/>
       <c r="G17" s="7">
         <v>14</v>
       </c>
-      <c r="H17" s="41"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="1"/>
       <c r="J17" s="4"/>
-      <c r="K17" s="28"/>
+      <c r="K17" s="37"/>
       <c r="L17" s="25"/>
       <c r="M17" s="8">
         <v>14</v>
       </c>
-      <c r="N17" s="41"/>
+      <c r="N17" s="36"/>
       <c r="O17" s="3"/>
       <c r="P17" s="4"/>
-      <c r="Q17" s="28"/>
+      <c r="Q17" s="37"/>
       <c r="R17" s="25"/>
       <c r="S17" s="7">
         <v>14</v>
       </c>
-      <c r="T17" s="41"/>
+      <c r="T17" s="36"/>
       <c r="U17" s="1"/>
       <c r="V17" s="4"/>
-      <c r="W17" s="28"/>
+      <c r="W17" s="37"/>
     </row>
     <row r="18" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
@@ -4831,48 +4834,48 @@
       <c r="A19" s="8">
         <v>16</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="30" t="s">
         <v>6</v>
       </c>
       <c r="F19" s="26"/>
       <c r="G19" s="7">
         <v>16</v>
       </c>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="4"/>
-      <c r="K19" s="29" t="s">
+      <c r="K19" s="30" t="s">
         <v>6</v>
       </c>
       <c r="L19" s="26"/>
       <c r="M19" s="8">
         <v>16</v>
       </c>
-      <c r="N19" s="42" t="s">
+      <c r="N19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="4"/>
-      <c r="Q19" s="29" t="s">
+      <c r="Q19" s="30" t="s">
         <v>6</v>
       </c>
       <c r="R19" s="26"/>
       <c r="S19" s="7">
         <v>16</v>
       </c>
-      <c r="T19" s="42" t="s">
+      <c r="T19" s="28" t="s">
         <v>6</v>
       </c>
       <c r="U19" s="1"/>
       <c r="V19" s="4"/>
-      <c r="W19" s="29" t="s">
+      <c r="W19" s="30" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4880,319 +4883,301 @@
       <c r="A20" s="8">
         <v>17</v>
       </c>
-      <c r="B20" s="42"/>
+      <c r="B20" s="28"/>
       <c r="C20" s="3"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="29"/>
+      <c r="E20" s="30"/>
       <c r="F20" s="26"/>
       <c r="G20" s="7">
         <v>17</v>
       </c>
-      <c r="H20" s="42"/>
+      <c r="H20" s="28"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-      <c r="K20" s="29"/>
+      <c r="K20" s="30"/>
       <c r="L20" s="26"/>
       <c r="M20" s="7">
         <v>17</v>
       </c>
-      <c r="N20" s="42"/>
+      <c r="N20" s="28"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="29"/>
+      <c r="Q20" s="30"/>
       <c r="R20" s="26"/>
       <c r="S20" s="7">
         <v>17</v>
       </c>
-      <c r="T20" s="42"/>
+      <c r="T20" s="28"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
-      <c r="W20" s="29"/>
+      <c r="W20" s="30"/>
     </row>
     <row r="21" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>18</v>
       </c>
-      <c r="B21" s="42"/>
+      <c r="B21" s="28"/>
       <c r="C21" s="3"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="29"/>
+      <c r="E21" s="30"/>
       <c r="F21" s="26"/>
       <c r="G21" s="7">
         <v>18</v>
       </c>
-      <c r="H21" s="42"/>
+      <c r="H21" s="28"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="29"/>
+      <c r="K21" s="30"/>
       <c r="L21" s="26"/>
       <c r="M21" s="7">
         <v>18</v>
       </c>
-      <c r="N21" s="42"/>
+      <c r="N21" s="28"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="29"/>
+      <c r="Q21" s="30"/>
       <c r="R21" s="26"/>
       <c r="S21" s="7">
         <v>18</v>
       </c>
-      <c r="T21" s="42"/>
+      <c r="T21" s="28"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
-      <c r="W21" s="29"/>
+      <c r="W21" s="30"/>
     </row>
     <row r="22" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>19</v>
       </c>
-      <c r="B22" s="42"/>
+      <c r="B22" s="28"/>
       <c r="C22" s="3"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="29"/>
+      <c r="E22" s="30"/>
       <c r="F22" s="26"/>
       <c r="G22" s="7">
         <v>19</v>
       </c>
-      <c r="H22" s="42"/>
+      <c r="H22" s="28"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-      <c r="K22" s="29"/>
+      <c r="K22" s="30"/>
       <c r="L22" s="26"/>
       <c r="M22" s="7">
         <v>19</v>
       </c>
-      <c r="N22" s="42"/>
+      <c r="N22" s="28"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
-      <c r="Q22" s="29"/>
+      <c r="Q22" s="30"/>
       <c r="R22" s="26"/>
       <c r="S22" s="7">
         <v>19</v>
       </c>
-      <c r="T22" s="42"/>
+      <c r="T22" s="28"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
-      <c r="W22" s="29"/>
+      <c r="W22" s="30"/>
     </row>
     <row r="23" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>20</v>
       </c>
-      <c r="B23" s="42"/>
+      <c r="B23" s="28"/>
       <c r="C23" s="3"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="29"/>
+      <c r="E23" s="30"/>
       <c r="F23" s="26"/>
       <c r="G23" s="7">
         <v>20</v>
       </c>
-      <c r="H23" s="42"/>
+      <c r="H23" s="28"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="29"/>
+      <c r="K23" s="30"/>
       <c r="L23" s="26"/>
       <c r="M23" s="7">
         <v>20</v>
       </c>
-      <c r="N23" s="42"/>
+      <c r="N23" s="28"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="29"/>
+      <c r="Q23" s="30"/>
       <c r="R23" s="26"/>
       <c r="S23" s="7">
         <v>20</v>
       </c>
-      <c r="T23" s="42"/>
+      <c r="T23" s="28"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
-      <c r="W23" s="29"/>
+      <c r="W23" s="30"/>
     </row>
     <row r="24" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>21</v>
       </c>
-      <c r="B24" s="42"/>
+      <c r="B24" s="28"/>
       <c r="C24" s="3"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="29"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="26"/>
       <c r="G24" s="7">
         <v>21</v>
       </c>
-      <c r="H24" s="42"/>
+      <c r="H24" s="28"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-      <c r="K24" s="29"/>
+      <c r="K24" s="30"/>
       <c r="L24" s="26"/>
       <c r="M24" s="7">
         <v>21</v>
       </c>
-      <c r="N24" s="42"/>
+      <c r="N24" s="28"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="29"/>
+      <c r="Q24" s="30"/>
       <c r="R24" s="26"/>
       <c r="S24" s="7">
         <v>21</v>
       </c>
-      <c r="T24" s="42"/>
+      <c r="T24" s="28"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
-      <c r="W24" s="29"/>
+      <c r="W24" s="30"/>
     </row>
     <row r="25" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>22</v>
       </c>
-      <c r="B25" s="42"/>
+      <c r="B25" s="28"/>
       <c r="C25" s="3"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="29"/>
+      <c r="E25" s="30"/>
       <c r="F25" s="26"/>
       <c r="G25" s="7">
         <v>22</v>
       </c>
-      <c r="H25" s="42"/>
+      <c r="H25" s="28"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="29"/>
+      <c r="K25" s="30"/>
       <c r="L25" s="26"/>
       <c r="M25" s="7">
         <v>22</v>
       </c>
-      <c r="N25" s="42"/>
+      <c r="N25" s="28"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="29"/>
+      <c r="Q25" s="30"/>
       <c r="R25" s="26"/>
       <c r="S25" s="7">
         <v>22</v>
       </c>
-      <c r="T25" s="42"/>
+      <c r="T25" s="28"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
-      <c r="W25" s="29"/>
+      <c r="W25" s="30"/>
     </row>
     <row r="26" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>23</v>
       </c>
-      <c r="B26" s="42"/>
+      <c r="B26" s="28"/>
       <c r="C26" s="3"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="29"/>
+      <c r="E26" s="30"/>
       <c r="F26" s="26"/>
       <c r="G26" s="7">
         <v>23</v>
       </c>
-      <c r="H26" s="42"/>
+      <c r="H26" s="28"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="29"/>
+      <c r="K26" s="30"/>
       <c r="L26" s="26"/>
       <c r="M26" s="7">
         <v>23</v>
       </c>
-      <c r="N26" s="42"/>
+      <c r="N26" s="28"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="29"/>
+      <c r="Q26" s="30"/>
       <c r="R26" s="26"/>
       <c r="S26" s="7">
         <v>23</v>
       </c>
-      <c r="T26" s="42"/>
+      <c r="T26" s="28"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
-      <c r="W26" s="29"/>
+      <c r="W26" s="30"/>
     </row>
     <row r="27" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>24</v>
       </c>
-      <c r="B27" s="42"/>
+      <c r="B27" s="28"/>
       <c r="C27" s="3"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="29"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="26"/>
       <c r="G27" s="7">
         <v>24</v>
       </c>
-      <c r="H27" s="42"/>
+      <c r="H27" s="28"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="29"/>
+      <c r="K27" s="30"/>
       <c r="L27" s="26"/>
       <c r="M27" s="7">
         <v>24</v>
       </c>
-      <c r="N27" s="42"/>
+      <c r="N27" s="28"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="29"/>
+      <c r="Q27" s="30"/>
       <c r="R27" s="26"/>
       <c r="S27" s="7">
         <v>24</v>
       </c>
-      <c r="T27" s="42"/>
+      <c r="T27" s="28"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
-      <c r="W27" s="29"/>
+      <c r="W27" s="30"/>
     </row>
     <row r="28" spans="1:23" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11">
         <v>25</v>
       </c>
-      <c r="B28" s="43"/>
+      <c r="B28" s="29"/>
       <c r="C28" s="12"/>
       <c r="D28" s="10"/>
-      <c r="E28" s="30"/>
+      <c r="E28" s="31"/>
       <c r="F28" s="27"/>
       <c r="G28" s="9">
         <v>25</v>
       </c>
-      <c r="H28" s="43"/>
+      <c r="H28" s="29"/>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
-      <c r="K28" s="30"/>
+      <c r="K28" s="31"/>
       <c r="L28" s="27"/>
       <c r="M28" s="9">
         <v>25</v>
       </c>
-      <c r="N28" s="43"/>
+      <c r="N28" s="29"/>
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
-      <c r="Q28" s="30"/>
+      <c r="Q28" s="31"/>
       <c r="R28" s="27"/>
       <c r="S28" s="9">
         <v>25</v>
       </c>
-      <c r="T28" s="43"/>
+      <c r="T28" s="29"/>
       <c r="U28" s="10"/>
       <c r="V28" s="10"/>
-      <c r="W28" s="30"/>
+      <c r="W28" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="T19:T28"/>
-    <mergeCell ref="K19:K28"/>
-    <mergeCell ref="N10:N17"/>
-    <mergeCell ref="N19:N28"/>
-    <mergeCell ref="Q10:Q17"/>
-    <mergeCell ref="Q19:Q28"/>
-    <mergeCell ref="K10:K17"/>
-    <mergeCell ref="N4:N9"/>
-    <mergeCell ref="Q4:Q9"/>
-    <mergeCell ref="T4:T9"/>
-    <mergeCell ref="W4:W9"/>
-    <mergeCell ref="T10:T17"/>
-    <mergeCell ref="B19:B28"/>
-    <mergeCell ref="E10:E17"/>
-    <mergeCell ref="E19:E28"/>
-    <mergeCell ref="H10:H17"/>
-    <mergeCell ref="H19:H28"/>
-    <mergeCell ref="W10:W17"/>
     <mergeCell ref="W19:W28"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="C2:D2"/>
@@ -5208,8 +5193,26 @@
     <mergeCell ref="K4:K9"/>
     <mergeCell ref="E4:E9"/>
     <mergeCell ref="B10:B17"/>
+    <mergeCell ref="B19:B28"/>
+    <mergeCell ref="E10:E17"/>
+    <mergeCell ref="E19:E28"/>
+    <mergeCell ref="H10:H17"/>
+    <mergeCell ref="H19:H28"/>
+    <mergeCell ref="N4:N9"/>
+    <mergeCell ref="Q4:Q9"/>
+    <mergeCell ref="T4:T9"/>
+    <mergeCell ref="W4:W9"/>
+    <mergeCell ref="T10:T17"/>
+    <mergeCell ref="W10:W17"/>
+    <mergeCell ref="T19:T28"/>
+    <mergeCell ref="K19:K28"/>
+    <mergeCell ref="N10:N17"/>
+    <mergeCell ref="N19:N28"/>
+    <mergeCell ref="Q10:Q17"/>
+    <mergeCell ref="Q19:Q28"/>
+    <mergeCell ref="K10:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="75" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="60" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>